--- a/datosIntentosSin0Output.xlsx
+++ b/datosIntentosSin0Output.xlsx
@@ -10859,7 +10859,7 @@
         <v>7</v>
       </c>
       <c r="E177" t="n">
-        <v>-17106.57</v>
+        <v>89.50700000000001</v>
       </c>
       <c r="F177" t="n">
         <v>100</v>
@@ -10906,7 +10906,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B178" t="n">
         <v>1</v>
@@ -10965,7 +10965,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B179" t="n">
         <v>1</v>
@@ -11024,7 +11024,7 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B180" t="n">
         <v>1</v>
@@ -11083,7 +11083,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B181" t="n">
         <v>3</v>
@@ -11142,7 +11142,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B182" t="n">
         <v>3</v>
@@ -11201,7 +11201,7 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B183" t="n">
         <v>3</v>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B184" t="n">
         <v>3</v>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B185" t="n">
         <v>3</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B186" t="n">
         <v>3</v>
@@ -11437,7 +11437,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B187" t="n">
         <v>3</v>
@@ -11496,7 +11496,7 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B188" t="n">
         <v>3</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B189" t="n">
         <v>3</v>
@@ -11614,7 +11614,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B190" t="n">
         <v>3</v>
@@ -11673,7 +11673,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B191" t="n">
         <v>1</v>
@@ -11732,7 +11732,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B192" t="n">
         <v>1</v>
@@ -11791,7 +11791,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B193" t="n">
         <v>1</v>
@@ -11850,7 +11850,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B194" t="n">
         <v>1</v>
@@ -11909,7 +11909,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B195" t="n">
         <v>3</v>
@@ -11968,7 +11968,7 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B196" t="n">
         <v>3</v>
@@ -12027,7 +12027,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B197" t="n">
         <v>3</v>
@@ -12086,7 +12086,7 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B198" t="n">
         <v>3</v>
@@ -12145,7 +12145,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B199" t="n">
         <v>3</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B200" t="n">
         <v>3</v>
@@ -12263,7 +12263,7 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B201" t="n">
         <v>3</v>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B202" t="n">
         <v>3</v>
@@ -12381,7 +12381,7 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B203" t="n">
         <v>3</v>
@@ -12440,7 +12440,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B204" t="n">
         <v>3</v>
@@ -12499,7 +12499,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B205" t="n">
         <v>3</v>
@@ -12558,7 +12558,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B206" t="n">
         <v>3</v>
@@ -12617,7 +12617,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B207" t="n">
         <v>1</v>
@@ -12676,7 +12676,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B208" t="n">
         <v>1</v>
@@ -12735,7 +12735,7 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B209" t="n">
         <v>1</v>
@@ -12794,7 +12794,7 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B210" t="n">
         <v>1</v>
@@ -12853,7 +12853,7 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B211" t="n">
         <v>1</v>
@@ -12912,7 +12912,7 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B212" t="n">
         <v>1</v>
@@ -12971,7 +12971,7 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B213" t="n">
         <v>1</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B214" t="n">
         <v>1</v>
@@ -13089,7 +13089,7 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B215" t="n">
         <v>1</v>
@@ -13148,7 +13148,7 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B216" t="n">
         <v>1</v>
@@ -13207,7 +13207,7 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B217" t="n">
         <v>1</v>
@@ -13266,7 +13266,7 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B218" t="n">
         <v>1</v>
@@ -13325,7 +13325,7 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B219" t="n">
         <v>1</v>
@@ -13384,7 +13384,7 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B220" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B221" t="n">
         <v>3</v>
@@ -13502,7 +13502,7 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B222" t="n">
         <v>3</v>
@@ -13561,7 +13561,7 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B223" t="n">
         <v>3</v>
@@ -13620,7 +13620,7 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B224" t="n">
         <v>3</v>
@@ -13679,7 +13679,7 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B225" t="n">
         <v>3</v>
@@ -13738,7 +13738,7 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B226" t="n">
         <v>3</v>
@@ -13797,7 +13797,7 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B227" t="n">
         <v>3</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B228" t="n">
         <v>3</v>
@@ -13915,7 +13915,7 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B229" t="n">
         <v>3</v>
@@ -13974,7 +13974,7 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B230" t="n">
         <v>1</v>
@@ -14033,7 +14033,7 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B231" t="n">
         <v>1</v>
@@ -14092,7 +14092,7 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B232" t="n">
         <v>1</v>
@@ -14151,7 +14151,7 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B233" t="n">
         <v>1</v>
@@ -14210,7 +14210,7 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B234" t="n">
         <v>1</v>
@@ -14269,7 +14269,7 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B235" t="n">
         <v>1</v>
@@ -14328,7 +14328,7 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B236" t="n">
         <v>1</v>
@@ -14387,7 +14387,7 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B237" t="n">
         <v>3</v>
@@ -14446,7 +14446,7 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B238" t="n">
         <v>3</v>
@@ -14505,7 +14505,7 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B239" t="n">
         <v>3</v>
@@ -14564,7 +14564,7 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B240" t="n">
         <v>3</v>
@@ -14623,7 +14623,7 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B241" t="n">
         <v>3</v>
@@ -14682,7 +14682,7 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B242" t="n">
         <v>3</v>
@@ -14741,7 +14741,7 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B243" t="n">
         <v>3</v>
@@ -14800,7 +14800,7 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B244" t="n">
         <v>3</v>
@@ -14859,7 +14859,7 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B245" t="n">
         <v>3</v>
@@ -14918,7 +14918,7 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B246" t="n">
         <v>3</v>
@@ -14977,7 +14977,7 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B247" t="n">
         <v>3</v>
@@ -15036,7 +15036,7 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B248" t="n">
         <v>3</v>
@@ -15095,7 +15095,7 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B249" t="n">
         <v>3</v>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B250" t="n">
         <v>3</v>
@@ -15213,7 +15213,7 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B251" t="n">
         <v>3</v>
@@ -15272,7 +15272,7 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B252" t="n">
         <v>3</v>
@@ -15331,7 +15331,7 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B253" t="n">
         <v>3</v>
@@ -15390,7 +15390,7 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B254" t="n">
         <v>3</v>
@@ -15449,7 +15449,7 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B255" t="n">
         <v>3</v>
@@ -15508,7 +15508,7 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B256" t="n">
         <v>3</v>
@@ -15567,7 +15567,7 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B257" t="n">
         <v>1</v>
@@ -15626,7 +15626,7 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B258" t="n">
         <v>1</v>
@@ -15685,7 +15685,7 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B259" t="n">
         <v>1</v>
@@ -15744,7 +15744,7 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B260" t="n">
         <v>1</v>
@@ -15803,7 +15803,7 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B261" t="n">
         <v>1</v>
@@ -15862,7 +15862,7 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B262" t="n">
         <v>1</v>
@@ -15921,7 +15921,7 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B263" t="n">
         <v>1</v>
@@ -15980,7 +15980,7 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B264" t="n">
         <v>1</v>
@@ -16039,7 +16039,7 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B265" t="n">
         <v>1</v>
@@ -16098,7 +16098,7 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B266" t="n">
         <v>1</v>
@@ -16157,7 +16157,7 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B267" t="n">
         <v>1</v>
@@ -16216,7 +16216,7 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B268" t="n">
         <v>1</v>
@@ -16275,7 +16275,7 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B269" t="n">
         <v>3</v>
@@ -16334,7 +16334,7 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B270" t="n">
         <v>3</v>
@@ -16393,7 +16393,7 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B271" t="n">
         <v>3</v>
@@ -16452,7 +16452,7 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B272" t="n">
         <v>3</v>
@@ -16511,7 +16511,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B273" t="n">
         <v>3</v>
@@ -16570,7 +16570,7 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B274" t="n">
         <v>3</v>
@@ -16629,7 +16629,7 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B275" t="n">
         <v>3</v>
@@ -16688,7 +16688,7 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B276" t="n">
         <v>3</v>
@@ -16747,7 +16747,7 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B277" t="n">
         <v>3</v>
@@ -16806,7 +16806,7 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B278" t="n">
         <v>3</v>
@@ -16865,7 +16865,7 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B279" t="n">
         <v>3</v>
@@ -16924,7 +16924,7 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B280" t="n">
         <v>3</v>
@@ -16983,7 +16983,7 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B281" t="n">
         <v>3</v>
@@ -17042,7 +17042,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B282" t="n">
         <v>3</v>
@@ -17101,7 +17101,7 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B283" t="n">
         <v>3</v>
@@ -17160,7 +17160,7 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B284" t="n">
         <v>3</v>
@@ -17219,7 +17219,7 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B285" t="n">
         <v>3</v>
@@ -17278,7 +17278,7 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B286" t="n">
         <v>3</v>
@@ -17337,7 +17337,7 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B287" t="n">
         <v>1</v>
@@ -17396,7 +17396,7 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B288" t="n">
         <v>1</v>
@@ -17455,7 +17455,7 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B289" t="n">
         <v>1</v>
@@ -17514,7 +17514,7 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B290" t="n">
         <v>1</v>
@@ -17573,7 +17573,7 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B291" t="n">
         <v>1</v>
@@ -17632,7 +17632,7 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B292" t="n">
         <v>1</v>
@@ -17691,7 +17691,7 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B293" t="n">
         <v>1</v>
@@ -17750,7 +17750,7 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B294" t="n">
         <v>1</v>
@@ -17809,7 +17809,7 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B295" t="n">
         <v>1</v>
@@ -17868,7 +17868,7 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B296" t="n">
         <v>3</v>
@@ -17927,7 +17927,7 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B297" t="n">
         <v>3</v>
@@ -17986,7 +17986,7 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B298" t="n">
         <v>3</v>
@@ -18045,7 +18045,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B299" t="n">
         <v>3</v>
@@ -18104,7 +18104,7 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B300" t="n">
         <v>3</v>
@@ -18163,7 +18163,7 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B301" t="n">
         <v>3</v>
@@ -18222,7 +18222,7 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B302" t="n">
         <v>3</v>
@@ -18281,7 +18281,7 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B303" t="n">
         <v>1</v>
@@ -18340,7 +18340,7 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B304" t="n">
         <v>1</v>
@@ -18399,7 +18399,7 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B305" t="n">
         <v>1</v>
@@ -18458,7 +18458,7 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B306" t="n">
         <v>1</v>
@@ -18517,7 +18517,7 @@
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B307" t="n">
         <v>1</v>
@@ -18576,7 +18576,7 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B308" t="n">
         <v>1</v>
@@ -18635,7 +18635,7 @@
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B309" t="n">
         <v>1</v>
@@ -18694,7 +18694,7 @@
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B310" t="n">
         <v>1</v>
@@ -18753,7 +18753,7 @@
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B311" t="n">
         <v>1</v>
@@ -18812,7 +18812,7 @@
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B312" t="n">
         <v>1</v>
@@ -18871,7 +18871,7 @@
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B313" t="n">
         <v>1</v>
@@ -18930,7 +18930,7 @@
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B314" t="n">
         <v>1</v>
@@ -18989,7 +18989,7 @@
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B315" t="n">
         <v>1</v>
@@ -19048,7 +19048,7 @@
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B316" t="n">
         <v>1</v>
@@ -19107,7 +19107,7 @@
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B317" t="n">
         <v>5</v>
@@ -19166,7 +19166,7 @@
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B318" t="n">
         <v>5</v>
@@ -19225,7 +19225,7 @@
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B319" t="n">
         <v>5</v>
@@ -19284,7 +19284,7 @@
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B320" t="n">
         <v>5</v>
@@ -19343,7 +19343,7 @@
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B321" t="n">
         <v>5</v>
@@ -19402,7 +19402,7 @@
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B322" t="n">
         <v>5</v>
@@ -19461,7 +19461,7 @@
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B323" t="n">
         <v>5</v>
@@ -19520,7 +19520,7 @@
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B324" t="n">
         <v>1</v>
@@ -19579,7 +19579,7 @@
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B325" t="n">
         <v>1</v>
@@ -19638,7 +19638,7 @@
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B326" t="n">
         <v>3</v>
@@ -19697,7 +19697,7 @@
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B327" t="n">
         <v>3</v>
@@ -19756,7 +19756,7 @@
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B328" t="n">
         <v>3</v>
@@ -19815,7 +19815,7 @@
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B329" t="n">
         <v>3</v>
@@ -19874,7 +19874,7 @@
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B330" t="n">
         <v>3</v>
@@ -19933,7 +19933,7 @@
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B331" t="n">
         <v>3</v>
@@ -19992,7 +19992,7 @@
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B332" t="n">
         <v>3</v>
@@ -20051,7 +20051,7 @@
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B333" t="n">
         <v>3</v>
@@ -20110,7 +20110,7 @@
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B334" t="n">
         <v>1</v>
@@ -20169,7 +20169,7 @@
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B335" t="n">
         <v>1</v>
@@ -20228,7 +20228,7 @@
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B336" t="n">
         <v>3</v>
@@ -20287,7 +20287,7 @@
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B337" t="n">
         <v>3</v>
@@ -20346,7 +20346,7 @@
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B338" t="n">
         <v>3</v>
@@ -20405,7 +20405,7 @@
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B339" t="n">
         <v>3</v>
@@ -20464,7 +20464,7 @@
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B340" t="n">
         <v>3</v>
@@ -20523,7 +20523,7 @@
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B341" t="n">
         <v>3</v>
@@ -20582,7 +20582,7 @@
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B342" t="n">
         <v>3</v>
@@ -20641,7 +20641,7 @@
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B343" t="n">
         <v>3</v>
@@ -20700,7 +20700,7 @@
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B344" t="n">
         <v>3</v>
@@ -20759,7 +20759,7 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B345" t="n">
         <v>3</v>
@@ -20818,7 +20818,7 @@
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B346" t="n">
         <v>1</v>
@@ -20877,7 +20877,7 @@
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B347" t="n">
         <v>1</v>
@@ -20936,7 +20936,7 @@
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B348" t="n">
         <v>1</v>
@@ -20995,7 +20995,7 @@
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B349" t="n">
         <v>1</v>
@@ -21054,7 +21054,7 @@
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B350" t="n">
         <v>1</v>
@@ -21113,7 +21113,7 @@
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B351" t="n">
         <v>3</v>
@@ -21172,7 +21172,7 @@
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B352" t="n">
         <v>3</v>
@@ -21231,7 +21231,7 @@
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B353" t="n">
         <v>3</v>
@@ -21290,7 +21290,7 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B354" t="n">
         <v>3</v>
@@ -21349,7 +21349,7 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B355" t="n">
         <v>3</v>
@@ -21408,7 +21408,7 @@
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B356" t="n">
         <v>3</v>
@@ -21467,7 +21467,7 @@
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B357" t="n">
         <v>3</v>
@@ -21526,7 +21526,7 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B358" t="n">
         <v>3</v>
@@ -21585,7 +21585,7 @@
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B359" t="n">
         <v>3</v>
@@ -21644,7 +21644,7 @@
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B360" t="n">
         <v>3</v>
@@ -21703,7 +21703,7 @@
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B361" t="n">
         <v>3</v>
@@ -21762,7 +21762,7 @@
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B362" t="n">
         <v>3</v>
@@ -21821,7 +21821,7 @@
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B363" t="n">
         <v>3</v>
@@ -21880,7 +21880,7 @@
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B364" t="n">
         <v>3</v>
@@ -21939,7 +21939,7 @@
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B365" t="n">
         <v>3</v>
@@ -21998,7 +21998,7 @@
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B366" t="n">
         <v>1</v>
@@ -22057,7 +22057,7 @@
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B367" t="n">
         <v>1</v>
@@ -22116,7 +22116,7 @@
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B368" t="n">
         <v>1</v>
@@ -22175,7 +22175,7 @@
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B369" t="n">
         <v>1</v>
@@ -22234,7 +22234,7 @@
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B370" t="n">
         <v>1</v>
@@ -22293,7 +22293,7 @@
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B371" t="n">
         <v>1</v>
@@ -22352,7 +22352,7 @@
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B372" t="n">
         <v>1</v>
@@ -22411,7 +22411,7 @@
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B373" t="n">
         <v>1</v>
@@ -22470,7 +22470,7 @@
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B374" t="n">
         <v>1</v>
@@ -22529,7 +22529,7 @@
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B375" t="n">
         <v>1</v>
@@ -22588,7 +22588,7 @@
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B376" t="n">
         <v>1</v>
@@ -22647,7 +22647,7 @@
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B377" t="n">
         <v>1</v>
@@ -22706,7 +22706,7 @@
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B378" t="n">
         <v>1</v>
@@ -22765,7 +22765,7 @@
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B379" t="n">
         <v>3</v>
@@ -22824,7 +22824,7 @@
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B380" t="n">
         <v>3</v>
@@ -22883,7 +22883,7 @@
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B381" t="n">
         <v>3</v>
@@ -22942,7 +22942,7 @@
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B382" t="n">
         <v>3</v>
@@ -23001,7 +23001,7 @@
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B383" t="n">
         <v>3</v>
@@ -23060,7 +23060,7 @@
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B384" t="n">
         <v>3</v>
@@ -23119,7 +23119,7 @@
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B385" t="n">
         <v>1</v>
@@ -23178,7 +23178,7 @@
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B386" t="n">
         <v>1</v>
@@ -23237,7 +23237,7 @@
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B387" t="n">
         <v>1</v>
@@ -23296,7 +23296,7 @@
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B388" t="n">
         <v>1</v>
@@ -23355,7 +23355,7 @@
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B389" t="n">
         <v>1</v>
@@ -23414,7 +23414,7 @@
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B390" t="n">
         <v>3</v>
@@ -23473,7 +23473,7 @@
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B391" t="n">
         <v>3</v>
@@ -23532,7 +23532,7 @@
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B392" t="n">
         <v>3</v>
@@ -23591,7 +23591,7 @@
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B393" t="n">
         <v>3</v>
@@ -23650,7 +23650,7 @@
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B394" t="n">
         <v>3</v>
@@ -23709,7 +23709,7 @@
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B395" t="n">
         <v>3</v>
@@ -23768,7 +23768,7 @@
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B396" t="n">
         <v>3</v>
@@ -23827,7 +23827,7 @@
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B397" t="n">
         <v>3</v>
@@ -23886,7 +23886,7 @@
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B398" t="n">
         <v>1</v>
@@ -23945,7 +23945,7 @@
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B399" t="n">
         <v>1</v>
@@ -24004,7 +24004,7 @@
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B400" t="n">
         <v>1</v>
@@ -24063,7 +24063,7 @@
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B401" t="n">
         <v>1</v>
@@ -24122,7 +24122,7 @@
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B402" t="n">
         <v>1</v>
@@ -24181,7 +24181,7 @@
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B403" t="n">
         <v>1</v>
@@ -24240,7 +24240,7 @@
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B404" t="n">
         <v>1</v>
@@ -24299,7 +24299,7 @@
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B405" t="n">
         <v>1</v>
@@ -24358,7 +24358,7 @@
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B406" t="n">
         <v>1</v>
@@ -24417,7 +24417,7 @@
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B407" t="n">
         <v>2</v>
@@ -24476,7 +24476,7 @@
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B408" t="n">
         <v>2</v>
@@ -24535,7 +24535,7 @@
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B409" t="n">
         <v>2</v>
@@ -24594,7 +24594,7 @@
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B410" t="n">
         <v>2</v>
@@ -24653,7 +24653,7 @@
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B411" t="n">
         <v>3</v>
@@ -24712,7 +24712,7 @@
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B412" t="n">
         <v>3</v>
@@ -24771,7 +24771,7 @@
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B413" t="n">
         <v>3</v>
@@ -24830,7 +24830,7 @@
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B414" t="n">
         <v>3</v>
@@ -24889,7 +24889,7 @@
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B415" t="n">
         <v>3</v>
@@ -24948,7 +24948,7 @@
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B416" t="n">
         <v>3</v>
@@ -25007,7 +25007,7 @@
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B417" t="n">
         <v>3</v>
@@ -25066,7 +25066,7 @@
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B418" t="n">
         <v>1</v>
@@ -25125,7 +25125,7 @@
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B419" t="n">
         <v>3</v>
@@ -25184,7 +25184,7 @@
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B420" t="n">
         <v>3</v>
@@ -25243,7 +25243,7 @@
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B421" t="n">
         <v>3</v>
@@ -25302,7 +25302,7 @@
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B422" t="n">
         <v>3</v>
@@ -25361,7 +25361,7 @@
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B423" t="n">
         <v>3</v>
@@ -25420,7 +25420,7 @@
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B424" t="n">
         <v>3</v>
@@ -25479,7 +25479,7 @@
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B425" t="n">
         <v>3</v>
@@ -25538,7 +25538,7 @@
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B426" t="n">
         <v>2</v>
@@ -25597,7 +25597,7 @@
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B427" t="n">
         <v>2</v>
@@ -25656,7 +25656,7 @@
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B428" t="n">
         <v>2</v>
@@ -25715,7 +25715,7 @@
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B429" t="n">
         <v>2</v>
@@ -25774,7 +25774,7 @@
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B430" t="n">
         <v>2</v>
@@ -25833,7 +25833,7 @@
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B431" t="n">
         <v>3</v>
@@ -25892,7 +25892,7 @@
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B432" t="n">
         <v>3</v>
@@ -25951,7 +25951,7 @@
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B433" t="n">
         <v>3</v>
@@ -26010,7 +26010,7 @@
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B434" t="n">
         <v>3</v>
@@ -26069,7 +26069,7 @@
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B435" t="n">
         <v>3</v>
@@ -26128,7 +26128,7 @@
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B436" t="n">
         <v>3</v>
@@ -26187,7 +26187,7 @@
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B437" t="n">
         <v>3</v>
@@ -26246,7 +26246,7 @@
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B438" t="n">
         <v>3</v>
@@ -26305,7 +26305,7 @@
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B439" t="n">
         <v>3</v>
@@ -26364,7 +26364,7 @@
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B440" t="n">
         <v>3</v>
@@ -26423,7 +26423,7 @@
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B441" t="n">
         <v>1</v>
@@ -26482,7 +26482,7 @@
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B442" t="n">
         <v>1</v>
@@ -26541,7 +26541,7 @@
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B443" t="n">
         <v>1</v>
@@ -26600,7 +26600,7 @@
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B444" t="n">
         <v>1</v>
@@ -26659,7 +26659,7 @@
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B445" t="n">
         <v>1</v>
@@ -26718,7 +26718,7 @@
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B446" t="n">
         <v>1</v>
@@ -26777,7 +26777,7 @@
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B447" t="n">
         <v>1</v>
@@ -26836,7 +26836,7 @@
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B448" t="n">
         <v>1</v>
@@ -26895,7 +26895,7 @@
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B449" t="n">
         <v>3</v>
@@ -26954,7 +26954,7 @@
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B450" t="n">
         <v>3</v>
@@ -27013,7 +27013,7 @@
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B451" t="n">
         <v>3</v>
@@ -27072,7 +27072,7 @@
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B452" t="n">
         <v>3</v>
@@ -27131,7 +27131,7 @@
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B453" t="n">
         <v>3</v>
@@ -27190,7 +27190,7 @@
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B454" t="n">
         <v>3</v>
@@ -27249,7 +27249,7 @@
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B455" t="n">
         <v>3</v>
@@ -27308,7 +27308,7 @@
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B456" t="n">
         <v>3</v>
@@ -27367,7 +27367,7 @@
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B457" t="n">
         <v>3</v>

--- a/datosIntentosSin0Output.xlsx
+++ b/datosIntentosSin0Output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S457"/>
+  <dimension ref="A1:U457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -578,6 +588,12 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -637,6 +653,12 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
+      <c r="T3" t="n">
+        <v>80</v>
+      </c>
+      <c r="U3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -694,6 +716,12 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -755,6 +783,12 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
+      <c r="T5" t="n">
+        <v>50</v>
+      </c>
+      <c r="U5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -814,6 +848,12 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
+      <c r="T6" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U6" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -873,6 +913,12 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
+      <c r="T7" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -932,6 +978,12 @@
       <c r="S8" t="n">
         <v>1</v>
       </c>
+      <c r="T8" t="n">
+        <v>100</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -991,6 +1043,12 @@
       <c r="S9" t="n">
         <v>1</v>
       </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1050,6 +1108,12 @@
       <c r="S10" t="n">
         <v>0</v>
       </c>
+      <c r="T10" t="n">
+        <v>75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1109,6 +1173,12 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1168,6 +1238,12 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
+      <c r="T12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U12" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1227,6 +1303,12 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
+      <c r="T13" t="n">
+        <v>75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1286,6 +1368,12 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
+      <c r="T14" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1345,6 +1433,12 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
+      <c r="T15" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U15" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1404,6 +1498,12 @@
       <c r="S16" t="n">
         <v>0</v>
       </c>
+      <c r="T16" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1463,6 +1563,12 @@
       <c r="S17" t="n">
         <v>1</v>
       </c>
+      <c r="T17" t="n">
+        <v>100</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1522,6 +1628,12 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
+      <c r="T18" t="n">
+        <v>50</v>
+      </c>
+      <c r="U18" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1581,6 +1693,12 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
+      <c r="T19" t="n">
+        <v>100</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1640,6 +1758,12 @@
       <c r="S20" t="n">
         <v>0</v>
       </c>
+      <c r="T20" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U20" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1699,6 +1823,12 @@
       <c r="S21" t="n">
         <v>0</v>
       </c>
+      <c r="T21" t="n">
+        <v>50</v>
+      </c>
+      <c r="U21" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1758,6 +1888,12 @@
       <c r="S22" t="n">
         <v>0</v>
       </c>
+      <c r="T22" t="n">
+        <v>100</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1817,6 +1953,12 @@
       <c r="S23" t="n">
         <v>0</v>
       </c>
+      <c r="T23" t="n">
+        <v>100</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1876,6 +2018,12 @@
       <c r="S24" t="n">
         <v>0</v>
       </c>
+      <c r="T24" t="n">
+        <v>50</v>
+      </c>
+      <c r="U24" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1935,6 +2083,12 @@
       <c r="S25" t="n">
         <v>0</v>
       </c>
+      <c r="T25" t="n">
+        <v>100</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1994,6 +2148,12 @@
       <c r="S26" t="n">
         <v>0</v>
       </c>
+      <c r="T26" t="n">
+        <v>100</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2053,6 +2213,12 @@
       <c r="S27" t="n">
         <v>0</v>
       </c>
+      <c r="T27" t="n">
+        <v>100</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2112,6 +2278,12 @@
       <c r="S28" t="n">
         <v>0</v>
       </c>
+      <c r="T28" t="n">
+        <v>100</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2171,6 +2343,12 @@
       <c r="S29" t="n">
         <v>1</v>
       </c>
+      <c r="T29" t="n">
+        <v>50</v>
+      </c>
+      <c r="U29" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2230,6 +2408,12 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
+      <c r="T30" t="n">
+        <v>100</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2289,6 +2473,12 @@
       <c r="S31" t="n">
         <v>0</v>
       </c>
+      <c r="T31" t="n">
+        <v>100</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2348,6 +2538,12 @@
       <c r="S32" t="n">
         <v>0</v>
       </c>
+      <c r="T32" t="n">
+        <v>100</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2407,6 +2603,12 @@
       <c r="S33" t="n">
         <v>0</v>
       </c>
+      <c r="T33" t="n">
+        <v>100</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2466,6 +2668,12 @@
       <c r="S34" t="n">
         <v>1</v>
       </c>
+      <c r="T34" t="n">
+        <v>100</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2525,6 +2733,12 @@
       <c r="S35" t="n">
         <v>0</v>
       </c>
+      <c r="T35" t="n">
+        <v>100</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2584,6 +2798,12 @@
       <c r="S36" t="n">
         <v>0</v>
       </c>
+      <c r="T36" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U36" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2643,6 +2863,12 @@
       <c r="S37" t="n">
         <v>0</v>
       </c>
+      <c r="T37" t="n">
+        <v>100</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2702,6 +2928,12 @@
       <c r="S38" t="n">
         <v>0</v>
       </c>
+      <c r="T38" t="n">
+        <v>100</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2761,6 +2993,12 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2820,6 +3058,12 @@
       <c r="S40" t="n">
         <v>1</v>
       </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2879,6 +3123,12 @@
       <c r="S41" t="n">
         <v>0</v>
       </c>
+      <c r="T41" t="n">
+        <v>100</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2938,6 +3188,12 @@
       <c r="S42" t="n">
         <v>1</v>
       </c>
+      <c r="T42" t="n">
+        <v>50</v>
+      </c>
+      <c r="U42" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2997,6 +3253,12 @@
       <c r="S43" t="n">
         <v>0</v>
       </c>
+      <c r="T43" t="n">
+        <v>100</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3056,6 +3318,12 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
+      <c r="T44" t="n">
+        <v>100</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3115,6 +3383,12 @@
       <c r="S45" t="n">
         <v>1</v>
       </c>
+      <c r="T45" t="n">
+        <v>100</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3174,6 +3448,12 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
+      <c r="T46" t="n">
+        <v>100</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3233,6 +3513,12 @@
       <c r="S47" t="n">
         <v>0</v>
       </c>
+      <c r="T47" t="n">
+        <v>100</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3292,6 +3578,12 @@
       <c r="S48" t="n">
         <v>0</v>
       </c>
+      <c r="T48" t="n">
+        <v>100</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3351,6 +3643,12 @@
       <c r="S49" t="n">
         <v>1</v>
       </c>
+      <c r="T49" t="n">
+        <v>100</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3410,6 +3708,12 @@
       <c r="S50" t="n">
         <v>2</v>
       </c>
+      <c r="T50" t="n">
+        <v>100</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3469,6 +3773,12 @@
       <c r="S51" t="n">
         <v>0</v>
       </c>
+      <c r="T51" t="n">
+        <v>75</v>
+      </c>
+      <c r="U51" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3528,6 +3838,12 @@
       <c r="S52" t="n">
         <v>0</v>
       </c>
+      <c r="T52" t="n">
+        <v>100</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -3587,6 +3903,12 @@
       <c r="S53" t="n">
         <v>0</v>
       </c>
+      <c r="T53" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U53" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -3646,6 +3968,12 @@
       <c r="S54" t="n">
         <v>0</v>
       </c>
+      <c r="T54" t="n">
+        <v>100</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -3705,6 +4033,12 @@
       <c r="S55" t="n">
         <v>0</v>
       </c>
+      <c r="T55" t="n">
+        <v>100</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -3764,6 +4098,12 @@
       <c r="S56" t="n">
         <v>0</v>
       </c>
+      <c r="T56" t="n">
+        <v>100</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -3823,6 +4163,12 @@
       <c r="S57" t="n">
         <v>0</v>
       </c>
+      <c r="T57" t="n">
+        <v>100</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -3882,6 +4228,12 @@
       <c r="S58" t="n">
         <v>0</v>
       </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -3941,6 +4293,12 @@
       <c r="S59" t="n">
         <v>0</v>
       </c>
+      <c r="T59" t="n">
+        <v>100</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4000,6 +4358,12 @@
       <c r="S60" t="n">
         <v>0</v>
       </c>
+      <c r="T60" t="n">
+        <v>100</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4059,6 +4423,12 @@
       <c r="S61" t="n">
         <v>0</v>
       </c>
+      <c r="T61" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U61" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -4118,6 +4488,12 @@
       <c r="S62" t="n">
         <v>0</v>
       </c>
+      <c r="T62" t="n">
+        <v>100</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -4177,6 +4553,12 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
+      <c r="T63" t="n">
+        <v>100</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4236,6 +4618,12 @@
       <c r="S64" t="n">
         <v>0</v>
       </c>
+      <c r="T64" t="n">
+        <v>100</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4295,6 +4683,12 @@
       <c r="S65" t="n">
         <v>0</v>
       </c>
+      <c r="T65" t="n">
+        <v>100</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4354,6 +4748,12 @@
       <c r="S66" t="n">
         <v>0</v>
       </c>
+      <c r="T66" t="n">
+        <v>100</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -4413,6 +4813,12 @@
       <c r="S67" t="n">
         <v>0</v>
       </c>
+      <c r="T67" t="n">
+        <v>25</v>
+      </c>
+      <c r="U67" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -4472,6 +4878,12 @@
       <c r="S68" t="n">
         <v>0</v>
       </c>
+      <c r="T68" t="n">
+        <v>50</v>
+      </c>
+      <c r="U68" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -4531,6 +4943,12 @@
       <c r="S69" t="n">
         <v>0</v>
       </c>
+      <c r="T69" t="n">
+        <v>100</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -4590,6 +5008,12 @@
       <c r="S70" t="n">
         <v>0</v>
       </c>
+      <c r="T70" t="n">
+        <v>100</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -4649,6 +5073,12 @@
       <c r="S71" t="n">
         <v>0</v>
       </c>
+      <c r="T71" t="n">
+        <v>100</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -4708,6 +5138,12 @@
       <c r="S72" t="n">
         <v>0</v>
       </c>
+      <c r="T72" t="n">
+        <v>100</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -4767,6 +5203,12 @@
       <c r="S73" t="n">
         <v>0</v>
       </c>
+      <c r="T73" t="n">
+        <v>100</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -4826,6 +5268,12 @@
       <c r="S74" t="n">
         <v>0</v>
       </c>
+      <c r="T74" t="n">
+        <v>50</v>
+      </c>
+      <c r="U74" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -4885,6 +5333,12 @@
       <c r="S75" t="n">
         <v>0</v>
       </c>
+      <c r="T75" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U75" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -4944,6 +5398,12 @@
       <c r="S76" t="n">
         <v>0</v>
       </c>
+      <c r="T76" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U76" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -5003,6 +5463,12 @@
       <c r="S77" t="n">
         <v>0</v>
       </c>
+      <c r="T77" t="n">
+        <v>100</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -5062,6 +5528,12 @@
       <c r="S78" t="n">
         <v>1</v>
       </c>
+      <c r="T78" t="n">
+        <v>50</v>
+      </c>
+      <c r="U78" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -5121,6 +5593,12 @@
       <c r="S79" t="n">
         <v>0</v>
       </c>
+      <c r="T79" t="n">
+        <v>100</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -5180,6 +5658,12 @@
       <c r="S80" t="n">
         <v>0</v>
       </c>
+      <c r="T80" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U80" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -5239,6 +5723,12 @@
       <c r="S81" t="n">
         <v>0</v>
       </c>
+      <c r="T81" t="n">
+        <v>100</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -5298,6 +5788,12 @@
       <c r="S82" t="n">
         <v>0</v>
       </c>
+      <c r="T82" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U82" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -5357,6 +5853,12 @@
       <c r="S83" t="n">
         <v>0</v>
       </c>
+      <c r="T83" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="U83" t="n">
+        <v>43.75</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -5416,6 +5918,12 @@
       <c r="S84" t="n">
         <v>0</v>
       </c>
+      <c r="T84" t="n">
+        <v>100</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -5475,6 +5983,12 @@
       <c r="S85" t="n">
         <v>0</v>
       </c>
+      <c r="T85" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="U85" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -5534,6 +6048,12 @@
       <c r="S86" t="n">
         <v>0</v>
       </c>
+      <c r="T86" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U86" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -5593,6 +6113,12 @@
       <c r="S87" t="n">
         <v>0</v>
       </c>
+      <c r="T87" t="n">
+        <v>100</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -5652,6 +6178,12 @@
       <c r="S88" t="n">
         <v>0</v>
       </c>
+      <c r="T88" t="n">
+        <v>100</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -5711,6 +6243,12 @@
       <c r="S89" t="n">
         <v>0</v>
       </c>
+      <c r="T89" t="n">
+        <v>100</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -5770,6 +6308,12 @@
       <c r="S90" t="n">
         <v>0</v>
       </c>
+      <c r="T90" t="n">
+        <v>100</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -5829,6 +6373,12 @@
       <c r="S91" t="n">
         <v>0</v>
       </c>
+      <c r="T91" t="n">
+        <v>100</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -5888,6 +6438,12 @@
       <c r="S92" t="n">
         <v>0</v>
       </c>
+      <c r="T92" t="n">
+        <v>60</v>
+      </c>
+      <c r="U92" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -5947,6 +6503,12 @@
       <c r="S93" t="n">
         <v>0</v>
       </c>
+      <c r="T93" t="n">
+        <v>100</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -6006,6 +6568,12 @@
       <c r="S94" t="n">
         <v>0</v>
       </c>
+      <c r="T94" t="n">
+        <v>100</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -6065,6 +6633,12 @@
       <c r="S95" t="n">
         <v>0</v>
       </c>
+      <c r="T95" t="n">
+        <v>100</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -6124,6 +6698,12 @@
       <c r="S96" t="n">
         <v>0</v>
       </c>
+      <c r="T96" t="n">
+        <v>100</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -6183,6 +6763,12 @@
       <c r="S97" t="n">
         <v>0</v>
       </c>
+      <c r="T97" t="n">
+        <v>75</v>
+      </c>
+      <c r="U97" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -6242,6 +6828,12 @@
       <c r="S98" t="n">
         <v>0</v>
       </c>
+      <c r="T98" t="n">
+        <v>100</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -6301,6 +6893,12 @@
       <c r="S99" t="n">
         <v>0</v>
       </c>
+      <c r="T99" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U99" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -6360,6 +6958,12 @@
       <c r="S100" t="n">
         <v>0</v>
       </c>
+      <c r="T100" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U100" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -6419,6 +7023,12 @@
       <c r="S101" t="n">
         <v>0</v>
       </c>
+      <c r="T101" t="n">
+        <v>100</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -6478,6 +7088,12 @@
       <c r="S102" t="n">
         <v>0</v>
       </c>
+      <c r="T102" t="n">
+        <v>100</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -6537,6 +7153,12 @@
       <c r="S103" t="n">
         <v>0</v>
       </c>
+      <c r="T103" t="n">
+        <v>100</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -6596,6 +7218,12 @@
       <c r="S104" t="n">
         <v>0</v>
       </c>
+      <c r="T104" t="n">
+        <v>100</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -6655,6 +7283,12 @@
       <c r="S105" t="n">
         <v>1</v>
       </c>
+      <c r="T105" t="n">
+        <v>80</v>
+      </c>
+      <c r="U105" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -6714,6 +7348,12 @@
       <c r="S106" t="n">
         <v>0</v>
       </c>
+      <c r="T106" t="n">
+        <v>80</v>
+      </c>
+      <c r="U106" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -6773,6 +7413,12 @@
       <c r="S107" t="n">
         <v>0</v>
       </c>
+      <c r="T107" t="n">
+        <v>100</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -6832,6 +7478,12 @@
       <c r="S108" t="n">
         <v>0</v>
       </c>
+      <c r="T108" t="n">
+        <v>100</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -6891,6 +7543,12 @@
       <c r="S109" t="n">
         <v>0</v>
       </c>
+      <c r="T109" t="n">
+        <v>100</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -6950,6 +7608,12 @@
       <c r="S110" t="n">
         <v>0</v>
       </c>
+      <c r="T110" t="n">
+        <v>75</v>
+      </c>
+      <c r="U110" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -7009,6 +7673,12 @@
       <c r="S111" t="n">
         <v>0</v>
       </c>
+      <c r="T111" t="n">
+        <v>100</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -7068,6 +7738,12 @@
       <c r="S112" t="n">
         <v>0</v>
       </c>
+      <c r="T112" t="n">
+        <v>80</v>
+      </c>
+      <c r="U112" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -7127,6 +7803,12 @@
       <c r="S113" t="n">
         <v>0</v>
       </c>
+      <c r="T113" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U113" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -7186,6 +7868,12 @@
       <c r="S114" t="n">
         <v>0</v>
       </c>
+      <c r="T114" t="n">
+        <v>100</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -7245,6 +7933,12 @@
       <c r="S115" t="n">
         <v>0</v>
       </c>
+      <c r="T115" t="n">
+        <v>100</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -7304,6 +7998,12 @@
       <c r="S116" t="n">
         <v>0</v>
       </c>
+      <c r="T116" t="n">
+        <v>100</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -7363,6 +8063,12 @@
       <c r="S117" t="n">
         <v>0</v>
       </c>
+      <c r="T117" t="n">
+        <v>100</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -7422,6 +8128,12 @@
       <c r="S118" t="n">
         <v>0</v>
       </c>
+      <c r="T118" t="n">
+        <v>75</v>
+      </c>
+      <c r="U118" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -7481,6 +8193,12 @@
       <c r="S119" t="n">
         <v>0</v>
       </c>
+      <c r="T119" t="n">
+        <v>100</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -7540,6 +8258,12 @@
       <c r="S120" t="n">
         <v>0</v>
       </c>
+      <c r="T120" t="n">
+        <v>50</v>
+      </c>
+      <c r="U120" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -7599,6 +8323,12 @@
       <c r="S121" t="n">
         <v>0</v>
       </c>
+      <c r="T121" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U121" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -7658,6 +8388,12 @@
       <c r="S122" t="n">
         <v>0</v>
       </c>
+      <c r="T122" t="n">
+        <v>100</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -7717,6 +8453,12 @@
       <c r="S123" t="n">
         <v>0</v>
       </c>
+      <c r="T123" t="n">
+        <v>100</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -7776,6 +8518,12 @@
       <c r="S124" t="n">
         <v>0</v>
       </c>
+      <c r="T124" t="n">
+        <v>100</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -7835,6 +8583,12 @@
       <c r="S125" t="n">
         <v>0</v>
       </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -7894,6 +8648,12 @@
       <c r="S126" t="n">
         <v>0</v>
       </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -7953,6 +8713,12 @@
       <c r="S127" t="n">
         <v>0</v>
       </c>
+      <c r="T127" t="n">
+        <v>100</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -8012,6 +8778,12 @@
       <c r="S128" t="n">
         <v>0</v>
       </c>
+      <c r="T128" t="n">
+        <v>100</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -8071,6 +8843,12 @@
       <c r="S129" t="n">
         <v>0</v>
       </c>
+      <c r="T129" t="n">
+        <v>100</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -8130,6 +8908,12 @@
       <c r="S130" t="n">
         <v>0</v>
       </c>
+      <c r="T130" t="n">
+        <v>100</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -8189,6 +8973,12 @@
       <c r="S131" t="n">
         <v>0</v>
       </c>
+      <c r="T131" t="n">
+        <v>100</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -8248,6 +9038,12 @@
       <c r="S132" t="n">
         <v>0</v>
       </c>
+      <c r="T132" t="n">
+        <v>100</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -8307,6 +9103,12 @@
       <c r="S133" t="n">
         <v>0</v>
       </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -8366,6 +9168,12 @@
       <c r="S134" t="n">
         <v>0</v>
       </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -8425,6 +9233,12 @@
       <c r="S135" t="n">
         <v>0</v>
       </c>
+      <c r="T135" t="n">
+        <v>100</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -8484,6 +9298,12 @@
       <c r="S136" t="n">
         <v>0</v>
       </c>
+      <c r="T136" t="n">
+        <v>100</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -8543,6 +9363,12 @@
       <c r="S137" t="n">
         <v>0</v>
       </c>
+      <c r="T137" t="n">
+        <v>100</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -8602,6 +9428,12 @@
       <c r="S138" t="n">
         <v>0</v>
       </c>
+      <c r="T138" t="n">
+        <v>100</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -8661,6 +9493,12 @@
       <c r="S139" t="n">
         <v>0</v>
       </c>
+      <c r="T139" t="n">
+        <v>100</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -8720,6 +9558,12 @@
       <c r="S140" t="n">
         <v>0</v>
       </c>
+      <c r="T140" t="n">
+        <v>100</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -8779,6 +9623,12 @@
       <c r="S141" t="n">
         <v>0</v>
       </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -8838,6 +9688,12 @@
       <c r="S142" t="n">
         <v>3</v>
       </c>
+      <c r="T142" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U142" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -8897,6 +9753,12 @@
       <c r="S143" t="n">
         <v>0</v>
       </c>
+      <c r="T143" t="n">
+        <v>100</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -8956,6 +9818,12 @@
       <c r="S144" t="n">
         <v>0</v>
       </c>
+      <c r="T144" t="n">
+        <v>50</v>
+      </c>
+      <c r="U144" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -9015,6 +9883,12 @@
       <c r="S145" t="n">
         <v>0</v>
       </c>
+      <c r="T145" t="n">
+        <v>100</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -9074,6 +9948,12 @@
       <c r="S146" t="n">
         <v>0</v>
       </c>
+      <c r="T146" t="n">
+        <v>100</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -9133,6 +10013,12 @@
       <c r="S147" t="n">
         <v>0</v>
       </c>
+      <c r="T147" t="n">
+        <v>100</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -9192,6 +10078,12 @@
       <c r="S148" t="n">
         <v>0</v>
       </c>
+      <c r="T148" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U148" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -9251,6 +10143,12 @@
       <c r="S149" t="n">
         <v>0</v>
       </c>
+      <c r="T149" t="n">
+        <v>75</v>
+      </c>
+      <c r="U149" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -9310,6 +10208,12 @@
       <c r="S150" t="n">
         <v>0</v>
       </c>
+      <c r="T150" t="n">
+        <v>80</v>
+      </c>
+      <c r="U150" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -9369,6 +10273,12 @@
       <c r="S151" t="n">
         <v>0</v>
       </c>
+      <c r="T151" t="n">
+        <v>75</v>
+      </c>
+      <c r="U151" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -9428,6 +10338,12 @@
       <c r="S152" t="n">
         <v>0</v>
       </c>
+      <c r="T152" t="n">
+        <v>75</v>
+      </c>
+      <c r="U152" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -9487,6 +10403,12 @@
       <c r="S153" t="n">
         <v>0</v>
       </c>
+      <c r="T153" t="n">
+        <v>100</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -9546,6 +10468,12 @@
       <c r="S154" t="n">
         <v>0</v>
       </c>
+      <c r="T154" t="n">
+        <v>100</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -9605,6 +10533,12 @@
       <c r="S155" t="n">
         <v>0</v>
       </c>
+      <c r="T155" t="n">
+        <v>100</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -9664,6 +10598,12 @@
       <c r="S156" t="n">
         <v>0</v>
       </c>
+      <c r="T156" t="n">
+        <v>50</v>
+      </c>
+      <c r="U156" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -9723,6 +10663,12 @@
       <c r="S157" t="n">
         <v>0</v>
       </c>
+      <c r="T157" t="n">
+        <v>100</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -9782,6 +10728,12 @@
       <c r="S158" t="n">
         <v>0</v>
       </c>
+      <c r="T158" t="n">
+        <v>100</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -9841,6 +10793,12 @@
       <c r="S159" t="n">
         <v>0</v>
       </c>
+      <c r="T159" t="n">
+        <v>100</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -9900,6 +10858,12 @@
       <c r="S160" t="n">
         <v>0</v>
       </c>
+      <c r="T160" t="n">
+        <v>100</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -9959,6 +10923,12 @@
       <c r="S161" t="n">
         <v>1</v>
       </c>
+      <c r="T161" t="n">
+        <v>100</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -10018,6 +10988,12 @@
       <c r="S162" t="n">
         <v>0</v>
       </c>
+      <c r="T162" t="n">
+        <v>100</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -10077,6 +11053,12 @@
       <c r="S163" t="n">
         <v>0</v>
       </c>
+      <c r="T163" t="n">
+        <v>100</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -10136,6 +11118,12 @@
       <c r="S164" t="n">
         <v>0</v>
       </c>
+      <c r="T164" t="n">
+        <v>100</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -10195,6 +11183,12 @@
       <c r="S165" t="n">
         <v>0</v>
       </c>
+      <c r="T165" t="n">
+        <v>100</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -10254,6 +11248,12 @@
       <c r="S166" t="n">
         <v>0</v>
       </c>
+      <c r="T166" t="n">
+        <v>100</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -10313,6 +11313,12 @@
       <c r="S167" t="n">
         <v>0</v>
       </c>
+      <c r="T167" t="n">
+        <v>100</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -10372,6 +11378,12 @@
       <c r="S168" t="n">
         <v>0</v>
       </c>
+      <c r="T168" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U168" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -10431,6 +11443,12 @@
       <c r="S169" t="n">
         <v>0</v>
       </c>
+      <c r="T169" t="n">
+        <v>100</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -10490,6 +11508,12 @@
       <c r="S170" t="n">
         <v>0</v>
       </c>
+      <c r="T170" t="n">
+        <v>100</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -10549,6 +11573,12 @@
       <c r="S171" t="n">
         <v>0</v>
       </c>
+      <c r="T171" t="n">
+        <v>50</v>
+      </c>
+      <c r="U171" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -10608,6 +11638,12 @@
       <c r="S172" t="n">
         <v>0</v>
       </c>
+      <c r="T172" t="n">
+        <v>100</v>
+      </c>
+      <c r="U172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -10667,6 +11703,12 @@
       <c r="S173" t="n">
         <v>0</v>
       </c>
+      <c r="T173" t="n">
+        <v>100</v>
+      </c>
+      <c r="U173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -10726,6 +11768,12 @@
       <c r="S174" t="n">
         <v>0</v>
       </c>
+      <c r="T174" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U174" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -10785,6 +11833,12 @@
       <c r="S175" t="n">
         <v>0</v>
       </c>
+      <c r="T175" t="n">
+        <v>75</v>
+      </c>
+      <c r="U175" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -10844,6 +11898,12 @@
       <c r="S176" t="n">
         <v>0</v>
       </c>
+      <c r="T176" t="n">
+        <v>75</v>
+      </c>
+      <c r="U176" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -10903,6 +11963,12 @@
       <c r="S177" t="n">
         <v>0</v>
       </c>
+      <c r="T177" t="n">
+        <v>100</v>
+      </c>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -10962,6 +12028,12 @@
       <c r="S178" t="n">
         <v>0</v>
       </c>
+      <c r="T178" t="n">
+        <v>100</v>
+      </c>
+      <c r="U178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -11021,6 +12093,12 @@
       <c r="S179" t="n">
         <v>0</v>
       </c>
+      <c r="T179" t="n">
+        <v>100</v>
+      </c>
+      <c r="U179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -11080,6 +12158,12 @@
       <c r="S180" t="n">
         <v>0</v>
       </c>
+      <c r="T180" t="n">
+        <v>100</v>
+      </c>
+      <c r="U180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -11139,6 +12223,12 @@
       <c r="S181" t="n">
         <v>0</v>
       </c>
+      <c r="T181" t="n">
+        <v>50</v>
+      </c>
+      <c r="U181" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -11198,6 +12288,12 @@
       <c r="S182" t="n">
         <v>0</v>
       </c>
+      <c r="T182" t="n">
+        <v>100</v>
+      </c>
+      <c r="U182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -11257,6 +12353,12 @@
       <c r="S183" t="n">
         <v>0</v>
       </c>
+      <c r="T183" t="n">
+        <v>100</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -11316,6 +12418,12 @@
       <c r="S184" t="n">
         <v>0</v>
       </c>
+      <c r="T184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -11375,6 +12483,12 @@
       <c r="S185" t="n">
         <v>0</v>
       </c>
+      <c r="T185" t="n">
+        <v>50</v>
+      </c>
+      <c r="U185" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -11434,6 +12548,12 @@
       <c r="S186" t="n">
         <v>0</v>
       </c>
+      <c r="T186" t="n">
+        <v>100</v>
+      </c>
+      <c r="U186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -11493,6 +12613,12 @@
       <c r="S187" t="n">
         <v>1</v>
       </c>
+      <c r="T187" t="n">
+        <v>100</v>
+      </c>
+      <c r="U187" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -11552,6 +12678,12 @@
       <c r="S188" t="n">
         <v>0</v>
       </c>
+      <c r="T188" t="n">
+        <v>100</v>
+      </c>
+      <c r="U188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -11611,6 +12743,12 @@
       <c r="S189" t="n">
         <v>0</v>
       </c>
+      <c r="T189" t="n">
+        <v>100</v>
+      </c>
+      <c r="U189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -11670,6 +12808,12 @@
       <c r="S190" t="n">
         <v>0</v>
       </c>
+      <c r="T190" t="n">
+        <v>60</v>
+      </c>
+      <c r="U190" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -11729,6 +12873,12 @@
       <c r="S191" t="n">
         <v>0</v>
       </c>
+      <c r="T191" t="n">
+        <v>50</v>
+      </c>
+      <c r="U191" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -11788,6 +12938,12 @@
       <c r="S192" t="n">
         <v>0</v>
       </c>
+      <c r="T192" t="n">
+        <v>50</v>
+      </c>
+      <c r="U192" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -11847,6 +13003,12 @@
       <c r="S193" t="n">
         <v>0</v>
       </c>
+      <c r="T193" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U193" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -11906,6 +13068,12 @@
       <c r="S194" t="n">
         <v>0</v>
       </c>
+      <c r="T194" t="n">
+        <v>100</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -11965,6 +13133,12 @@
       <c r="S195" t="n">
         <v>0</v>
       </c>
+      <c r="T195" t="n">
+        <v>100</v>
+      </c>
+      <c r="U195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -12024,6 +13198,12 @@
       <c r="S196" t="n">
         <v>0</v>
       </c>
+      <c r="T196" t="n">
+        <v>100</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -12083,6 +13263,12 @@
       <c r="S197" t="n">
         <v>0</v>
       </c>
+      <c r="T197" t="n">
+        <v>100</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -12142,6 +13328,12 @@
       <c r="S198" t="n">
         <v>0</v>
       </c>
+      <c r="T198" t="n">
+        <v>100</v>
+      </c>
+      <c r="U198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -12201,6 +13393,12 @@
       <c r="S199" t="n">
         <v>1</v>
       </c>
+      <c r="T199" t="n">
+        <v>100</v>
+      </c>
+      <c r="U199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -12260,6 +13458,12 @@
       <c r="S200" t="n">
         <v>0</v>
       </c>
+      <c r="T200" t="n">
+        <v>100</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -12319,6 +13523,12 @@
       <c r="S201" t="n">
         <v>0</v>
       </c>
+      <c r="T201" t="n">
+        <v>100</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -12378,6 +13588,12 @@
       <c r="S202" t="n">
         <v>0</v>
       </c>
+      <c r="T202" t="n">
+        <v>100</v>
+      </c>
+      <c r="U202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -12437,6 +13653,12 @@
       <c r="S203" t="n">
         <v>0</v>
       </c>
+      <c r="T203" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U203" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -12496,6 +13718,12 @@
       <c r="S204" t="n">
         <v>0</v>
       </c>
+      <c r="T204" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U204" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -12555,6 +13783,12 @@
       <c r="S205" t="n">
         <v>0</v>
       </c>
+      <c r="T205" t="n">
+        <v>50</v>
+      </c>
+      <c r="U205" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -12614,6 +13848,12 @@
       <c r="S206" t="n">
         <v>0</v>
       </c>
+      <c r="T206" t="n">
+        <v>75</v>
+      </c>
+      <c r="U206" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -12673,6 +13913,12 @@
       <c r="S207" t="n">
         <v>0</v>
       </c>
+      <c r="T207" t="n">
+        <v>50</v>
+      </c>
+      <c r="U207" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -12732,6 +13978,12 @@
       <c r="S208" t="n">
         <v>0</v>
       </c>
+      <c r="T208" t="n">
+        <v>100</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -12791,6 +14043,12 @@
       <c r="S209" t="n">
         <v>0</v>
       </c>
+      <c r="T209" t="n">
+        <v>100</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -12850,6 +14108,12 @@
       <c r="S210" t="n">
         <v>0</v>
       </c>
+      <c r="T210" t="n">
+        <v>75</v>
+      </c>
+      <c r="U210" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -12909,6 +14173,12 @@
       <c r="S211" t="n">
         <v>0</v>
       </c>
+      <c r="T211" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U211" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -12968,6 +14238,12 @@
       <c r="S212" t="n">
         <v>0</v>
       </c>
+      <c r="T212" t="n">
+        <v>100</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -13027,6 +14303,12 @@
       <c r="S213" t="n">
         <v>0</v>
       </c>
+      <c r="T213" t="n">
+        <v>100</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -13086,6 +14368,12 @@
       <c r="S214" t="n">
         <v>0</v>
       </c>
+      <c r="T214" t="n">
+        <v>100</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -13145,6 +14433,12 @@
       <c r="S215" t="n">
         <v>0</v>
       </c>
+      <c r="T215" t="n">
+        <v>100</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -13204,6 +14498,12 @@
       <c r="S216" t="n">
         <v>0</v>
       </c>
+      <c r="T216" t="n">
+        <v>100</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -13263,6 +14563,12 @@
       <c r="S217" t="n">
         <v>0</v>
       </c>
+      <c r="T217" t="n">
+        <v>50</v>
+      </c>
+      <c r="U217" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -13322,6 +14628,12 @@
       <c r="S218" t="n">
         <v>0</v>
       </c>
+      <c r="T218" t="n">
+        <v>100</v>
+      </c>
+      <c r="U218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -13381,6 +14693,12 @@
       <c r="S219" t="n">
         <v>0</v>
       </c>
+      <c r="T219" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U219" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -13440,6 +14758,12 @@
       <c r="S220" t="n">
         <v>0</v>
       </c>
+      <c r="T220" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U220" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -13499,6 +14823,12 @@
       <c r="S221" t="n">
         <v>0</v>
       </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -13558,6 +14888,12 @@
       <c r="S222" t="n">
         <v>0</v>
       </c>
+      <c r="T222" t="n">
+        <v>100</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -13617,6 +14953,12 @@
       <c r="S223" t="n">
         <v>0</v>
       </c>
+      <c r="T223" t="n">
+        <v>100</v>
+      </c>
+      <c r="U223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -13676,6 +15018,12 @@
       <c r="S224" t="n">
         <v>0</v>
       </c>
+      <c r="T224" t="n">
+        <v>100</v>
+      </c>
+      <c r="U224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -13735,6 +15083,12 @@
       <c r="S225" t="n">
         <v>0</v>
       </c>
+      <c r="T225" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U225" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -13794,6 +15148,12 @@
       <c r="S226" t="n">
         <v>2</v>
       </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -13853,6 +15213,12 @@
       <c r="S227" t="n">
         <v>0</v>
       </c>
+      <c r="T227" t="n">
+        <v>73.3333333333333</v>
+      </c>
+      <c r="U227" t="n">
+        <v>26.6666666666666</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -13912,6 +15278,12 @@
       <c r="S228" t="n">
         <v>0</v>
       </c>
+      <c r="T228" t="n">
+        <v>100</v>
+      </c>
+      <c r="U228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -13971,6 +15343,12 @@
       <c r="S229" t="n">
         <v>0</v>
       </c>
+      <c r="T229" t="n">
+        <v>80</v>
+      </c>
+      <c r="U229" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -14030,6 +15408,12 @@
       <c r="S230" t="n">
         <v>0</v>
       </c>
+      <c r="T230" t="n">
+        <v>100</v>
+      </c>
+      <c r="U230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -14089,6 +15473,12 @@
       <c r="S231" t="n">
         <v>0</v>
       </c>
+      <c r="T231" t="n">
+        <v>100</v>
+      </c>
+      <c r="U231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -14148,6 +15538,12 @@
       <c r="S232" t="n">
         <v>2</v>
       </c>
+      <c r="T232" t="n">
+        <v>50</v>
+      </c>
+      <c r="U232" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -14207,6 +15603,12 @@
       <c r="S233" t="n">
         <v>0</v>
       </c>
+      <c r="T233" t="n">
+        <v>100</v>
+      </c>
+      <c r="U233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -14266,6 +15668,12 @@
       <c r="S234" t="n">
         <v>0</v>
       </c>
+      <c r="T234" t="n">
+        <v>100</v>
+      </c>
+      <c r="U234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -14325,6 +15733,12 @@
       <c r="S235" t="n">
         <v>0</v>
       </c>
+      <c r="T235" t="n">
+        <v>100</v>
+      </c>
+      <c r="U235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -14384,6 +15798,12 @@
       <c r="S236" t="n">
         <v>0</v>
       </c>
+      <c r="T236" t="n">
+        <v>100</v>
+      </c>
+      <c r="U236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -14443,6 +15863,12 @@
       <c r="S237" t="n">
         <v>0</v>
       </c>
+      <c r="T237" t="n">
+        <v>100</v>
+      </c>
+      <c r="U237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -14502,6 +15928,12 @@
       <c r="S238" t="n">
         <v>0</v>
       </c>
+      <c r="T238" t="n">
+        <v>100</v>
+      </c>
+      <c r="U238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -14561,6 +15993,12 @@
       <c r="S239" t="n">
         <v>0</v>
       </c>
+      <c r="T239" t="n">
+        <v>100</v>
+      </c>
+      <c r="U239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -14620,6 +16058,12 @@
       <c r="S240" t="n">
         <v>0</v>
       </c>
+      <c r="T240" t="n">
+        <v>100</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -14679,6 +16123,12 @@
       <c r="S241" t="n">
         <v>1</v>
       </c>
+      <c r="T241" t="n">
+        <v>100</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -14738,6 +16188,12 @@
       <c r="S242" t="n">
         <v>0</v>
       </c>
+      <c r="T242" t="n">
+        <v>100</v>
+      </c>
+      <c r="U242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -14797,6 +16253,12 @@
       <c r="S243" t="n">
         <v>0</v>
       </c>
+      <c r="T243" t="n">
+        <v>100</v>
+      </c>
+      <c r="U243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -14856,6 +16318,12 @@
       <c r="S244" t="n">
         <v>0</v>
       </c>
+      <c r="T244" t="n">
+        <v>100</v>
+      </c>
+      <c r="U244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -14915,6 +16383,12 @@
       <c r="S245" t="n">
         <v>0</v>
       </c>
+      <c r="T245" t="n">
+        <v>100</v>
+      </c>
+      <c r="U245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -14974,6 +16448,12 @@
       <c r="S246" t="n">
         <v>0</v>
       </c>
+      <c r="T246" t="n">
+        <v>50</v>
+      </c>
+      <c r="U246" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -15033,6 +16513,12 @@
       <c r="S247" t="n">
         <v>0</v>
       </c>
+      <c r="T247" t="n">
+        <v>100</v>
+      </c>
+      <c r="U247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -15092,6 +16578,12 @@
       <c r="S248" t="n">
         <v>0</v>
       </c>
+      <c r="T248" t="n">
+        <v>50</v>
+      </c>
+      <c r="U248" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -15151,6 +16643,12 @@
       <c r="S249" t="n">
         <v>0</v>
       </c>
+      <c r="T249" t="n">
+        <v>50</v>
+      </c>
+      <c r="U249" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -15210,6 +16708,12 @@
       <c r="S250" t="n">
         <v>0</v>
       </c>
+      <c r="T250" t="n">
+        <v>0</v>
+      </c>
+      <c r="U250" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -15269,6 +16773,12 @@
       <c r="S251" t="n">
         <v>0</v>
       </c>
+      <c r="T251" t="n">
+        <v>50</v>
+      </c>
+      <c r="U251" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -15328,6 +16838,12 @@
       <c r="S252" t="n">
         <v>0</v>
       </c>
+      <c r="T252" t="n">
+        <v>100</v>
+      </c>
+      <c r="U252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -15387,6 +16903,12 @@
       <c r="S253" t="n">
         <v>0</v>
       </c>
+      <c r="T253" t="n">
+        <v>100</v>
+      </c>
+      <c r="U253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -15446,6 +16968,12 @@
       <c r="S254" t="n">
         <v>0</v>
       </c>
+      <c r="T254" t="n">
+        <v>50</v>
+      </c>
+      <c r="U254" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -15505,6 +17033,12 @@
       <c r="S255" t="n">
         <v>0</v>
       </c>
+      <c r="T255" t="n">
+        <v>100</v>
+      </c>
+      <c r="U255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -15564,6 +17098,12 @@
       <c r="S256" t="n">
         <v>1</v>
       </c>
+      <c r="T256" t="n">
+        <v>100</v>
+      </c>
+      <c r="U256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -15623,6 +17163,12 @@
       <c r="S257" t="n">
         <v>0</v>
       </c>
+      <c r="T257" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U257" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -15682,6 +17228,12 @@
       <c r="S258" t="n">
         <v>0</v>
       </c>
+      <c r="T258" t="n">
+        <v>100</v>
+      </c>
+      <c r="U258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -15741,6 +17293,12 @@
       <c r="S259" t="n">
         <v>0</v>
       </c>
+      <c r="T259" t="n">
+        <v>100</v>
+      </c>
+      <c r="U259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -15800,6 +17358,12 @@
       <c r="S260" t="n">
         <v>0</v>
       </c>
+      <c r="T260" t="n">
+        <v>75</v>
+      </c>
+      <c r="U260" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -15859,6 +17423,12 @@
       <c r="S261" t="n">
         <v>0</v>
       </c>
+      <c r="T261" t="n">
+        <v>100</v>
+      </c>
+      <c r="U261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -15918,6 +17488,12 @@
       <c r="S262" t="n">
         <v>0</v>
       </c>
+      <c r="T262" t="n">
+        <v>100</v>
+      </c>
+      <c r="U262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -15977,6 +17553,12 @@
       <c r="S263" t="n">
         <v>0</v>
       </c>
+      <c r="T263" t="n">
+        <v>100</v>
+      </c>
+      <c r="U263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -16036,6 +17618,12 @@
       <c r="S264" t="n">
         <v>0</v>
       </c>
+      <c r="T264" t="n">
+        <v>100</v>
+      </c>
+      <c r="U264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -16095,6 +17683,12 @@
       <c r="S265" t="n">
         <v>1</v>
       </c>
+      <c r="T265" t="n">
+        <v>100</v>
+      </c>
+      <c r="U265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -16154,6 +17748,12 @@
       <c r="S266" t="n">
         <v>0</v>
       </c>
+      <c r="T266" t="n">
+        <v>80</v>
+      </c>
+      <c r="U266" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -16213,6 +17813,12 @@
       <c r="S267" t="n">
         <v>0</v>
       </c>
+      <c r="T267" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U267" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -16272,6 +17878,12 @@
       <c r="S268" t="n">
         <v>0</v>
       </c>
+      <c r="T268" t="n">
+        <v>100</v>
+      </c>
+      <c r="U268" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -16331,6 +17943,12 @@
       <c r="S269" t="n">
         <v>0</v>
       </c>
+      <c r="T269" t="n">
+        <v>100</v>
+      </c>
+      <c r="U269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -16390,6 +18008,12 @@
       <c r="S270" t="n">
         <v>0</v>
       </c>
+      <c r="T270" t="n">
+        <v>100</v>
+      </c>
+      <c r="U270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -16449,6 +18073,12 @@
       <c r="S271" t="n">
         <v>0</v>
       </c>
+      <c r="T271" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U271" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -16508,6 +18138,12 @@
       <c r="S272" t="n">
         <v>0</v>
       </c>
+      <c r="T272" t="n">
+        <v>100</v>
+      </c>
+      <c r="U272" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -16567,6 +18203,12 @@
       <c r="S273" t="n">
         <v>0</v>
       </c>
+      <c r="T273" t="n">
+        <v>100</v>
+      </c>
+      <c r="U273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -16626,6 +18268,12 @@
       <c r="S274" t="n">
         <v>0</v>
       </c>
+      <c r="T274" t="n">
+        <v>50</v>
+      </c>
+      <c r="U274" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -16685,6 +18333,12 @@
       <c r="S275" t="n">
         <v>0</v>
       </c>
+      <c r="T275" t="n">
+        <v>100</v>
+      </c>
+      <c r="U275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -16744,6 +18398,12 @@
       <c r="S276" t="n">
         <v>0</v>
       </c>
+      <c r="T276" t="n">
+        <v>100</v>
+      </c>
+      <c r="U276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -16803,6 +18463,12 @@
       <c r="S277" t="n">
         <v>0</v>
       </c>
+      <c r="T277" t="n">
+        <v>100</v>
+      </c>
+      <c r="U277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -16862,6 +18528,12 @@
       <c r="S278" t="n">
         <v>0</v>
       </c>
+      <c r="T278" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U278" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -16921,6 +18593,12 @@
       <c r="S279" t="n">
         <v>0</v>
       </c>
+      <c r="T279" t="n">
+        <v>100</v>
+      </c>
+      <c r="U279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -16980,6 +18658,12 @@
       <c r="S280" t="n">
         <v>1</v>
       </c>
+      <c r="T280" t="n">
+        <v>100</v>
+      </c>
+      <c r="U280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -17039,6 +18723,12 @@
       <c r="S281" t="n">
         <v>0</v>
       </c>
+      <c r="T281" t="n">
+        <v>50</v>
+      </c>
+      <c r="U281" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -17098,6 +18788,12 @@
       <c r="S282" t="n">
         <v>0</v>
       </c>
+      <c r="T282" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U282" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -17157,6 +18853,12 @@
       <c r="S283" t="n">
         <v>0</v>
       </c>
+      <c r="T283" t="n">
+        <v>100</v>
+      </c>
+      <c r="U283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -17216,6 +18918,12 @@
       <c r="S284" t="n">
         <v>1</v>
       </c>
+      <c r="T284" t="n">
+        <v>75</v>
+      </c>
+      <c r="U284" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -17275,6 +18983,12 @@
       <c r="S285" t="n">
         <v>0</v>
       </c>
+      <c r="T285" t="n">
+        <v>100</v>
+      </c>
+      <c r="U285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -17334,6 +19048,12 @@
       <c r="S286" t="n">
         <v>0</v>
       </c>
+      <c r="T286" t="n">
+        <v>100</v>
+      </c>
+      <c r="U286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -17393,6 +19113,12 @@
       <c r="S287" t="n">
         <v>0</v>
       </c>
+      <c r="T287" t="n">
+        <v>100</v>
+      </c>
+      <c r="U287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -17452,6 +19178,12 @@
       <c r="S288" t="n">
         <v>0</v>
       </c>
+      <c r="T288" t="n">
+        <v>100</v>
+      </c>
+      <c r="U288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -17511,6 +19243,12 @@
       <c r="S289" t="n">
         <v>0</v>
       </c>
+      <c r="T289" t="n">
+        <v>100</v>
+      </c>
+      <c r="U289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -17570,6 +19308,12 @@
       <c r="S290" t="n">
         <v>0</v>
       </c>
+      <c r="T290" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U290" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -17629,6 +19373,12 @@
       <c r="S291" t="n">
         <v>0</v>
       </c>
+      <c r="T291" t="n">
+        <v>100</v>
+      </c>
+      <c r="U291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -17688,6 +19438,12 @@
       <c r="S292" t="n">
         <v>1</v>
       </c>
+      <c r="T292" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U292" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -17747,6 +19503,12 @@
       <c r="S293" t="n">
         <v>0</v>
       </c>
+      <c r="T293" t="n">
+        <v>100</v>
+      </c>
+      <c r="U293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -17806,6 +19568,12 @@
       <c r="S294" t="n">
         <v>0</v>
       </c>
+      <c r="T294" t="n">
+        <v>60</v>
+      </c>
+      <c r="U294" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -17865,6 +19633,12 @@
       <c r="S295" t="n">
         <v>0</v>
       </c>
+      <c r="T295" t="n">
+        <v>100</v>
+      </c>
+      <c r="U295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -17924,6 +19698,12 @@
       <c r="S296" t="n">
         <v>0</v>
       </c>
+      <c r="T296" t="n">
+        <v>75</v>
+      </c>
+      <c r="U296" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -17983,6 +19763,12 @@
       <c r="S297" t="n">
         <v>0</v>
       </c>
+      <c r="T297" t="n">
+        <v>100</v>
+      </c>
+      <c r="U297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -18042,6 +19828,12 @@
       <c r="S298" t="n">
         <v>2</v>
       </c>
+      <c r="T298" t="n">
+        <v>100</v>
+      </c>
+      <c r="U298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -18101,6 +19893,12 @@
       <c r="S299" t="n">
         <v>0</v>
       </c>
+      <c r="T299" t="n">
+        <v>100</v>
+      </c>
+      <c r="U299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -18160,6 +19958,12 @@
       <c r="S300" t="n">
         <v>0</v>
       </c>
+      <c r="T300" t="n">
+        <v>100</v>
+      </c>
+      <c r="U300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -18219,6 +20023,12 @@
       <c r="S301" t="n">
         <v>0</v>
       </c>
+      <c r="T301" t="n">
+        <v>100</v>
+      </c>
+      <c r="U301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -18278,6 +20088,12 @@
       <c r="S302" t="n">
         <v>0</v>
       </c>
+      <c r="T302" t="n">
+        <v>100</v>
+      </c>
+      <c r="U302" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -18337,6 +20153,12 @@
       <c r="S303" t="n">
         <v>0</v>
       </c>
+      <c r="T303" t="n">
+        <v>75</v>
+      </c>
+      <c r="U303" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -18396,6 +20218,12 @@
       <c r="S304" t="n">
         <v>1</v>
       </c>
+      <c r="T304" t="n">
+        <v>100</v>
+      </c>
+      <c r="U304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -18455,6 +20283,12 @@
       <c r="S305" t="n">
         <v>0</v>
       </c>
+      <c r="T305" t="n">
+        <v>100</v>
+      </c>
+      <c r="U305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -18514,6 +20348,12 @@
       <c r="S306" t="n">
         <v>0</v>
       </c>
+      <c r="T306" t="n">
+        <v>75</v>
+      </c>
+      <c r="U306" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -18573,6 +20413,12 @@
       <c r="S307" t="n">
         <v>0</v>
       </c>
+      <c r="T307" t="n">
+        <v>50</v>
+      </c>
+      <c r="U307" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -18632,6 +20478,12 @@
       <c r="S308" t="n">
         <v>0</v>
       </c>
+      <c r="T308" t="n">
+        <v>100</v>
+      </c>
+      <c r="U308" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -18691,6 +20543,12 @@
       <c r="S309" t="n">
         <v>0</v>
       </c>
+      <c r="T309" t="n">
+        <v>100</v>
+      </c>
+      <c r="U309" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -18750,6 +20608,12 @@
       <c r="S310" t="n">
         <v>0</v>
       </c>
+      <c r="T310" t="n">
+        <v>100</v>
+      </c>
+      <c r="U310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -18809,6 +20673,12 @@
       <c r="S311" t="n">
         <v>0</v>
       </c>
+      <c r="T311" t="n">
+        <v>50</v>
+      </c>
+      <c r="U311" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
@@ -18868,6 +20738,12 @@
       <c r="S312" t="n">
         <v>0</v>
       </c>
+      <c r="T312" t="n">
+        <v>50</v>
+      </c>
+      <c r="U312" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
@@ -18927,6 +20803,12 @@
       <c r="S313" t="n">
         <v>0</v>
       </c>
+      <c r="T313" t="n">
+        <v>100</v>
+      </c>
+      <c r="U313" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
@@ -18986,6 +20868,12 @@
       <c r="S314" t="n">
         <v>0</v>
       </c>
+      <c r="T314" t="n">
+        <v>100</v>
+      </c>
+      <c r="U314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
@@ -19045,6 +20933,12 @@
       <c r="S315" t="n">
         <v>0</v>
       </c>
+      <c r="T315" t="n">
+        <v>100</v>
+      </c>
+      <c r="U315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
@@ -19104,6 +20998,12 @@
       <c r="S316" t="n">
         <v>0</v>
       </c>
+      <c r="T316" t="n">
+        <v>100</v>
+      </c>
+      <c r="U316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -19163,6 +21063,12 @@
       <c r="S317" t="n">
         <v>0</v>
       </c>
+      <c r="T317" t="n">
+        <v>100</v>
+      </c>
+      <c r="U317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -19222,6 +21128,12 @@
       <c r="S318" t="n">
         <v>0</v>
       </c>
+      <c r="T318" t="n">
+        <v>0</v>
+      </c>
+      <c r="U318" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -19281,6 +21193,12 @@
       <c r="S319" t="n">
         <v>0</v>
       </c>
+      <c r="T319" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U319" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -19340,6 +21258,12 @@
       <c r="S320" t="n">
         <v>0</v>
       </c>
+      <c r="T320" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="U320" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -19399,6 +21323,12 @@
       <c r="S321" t="n">
         <v>2</v>
       </c>
+      <c r="T321" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U321" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -19458,6 +21388,12 @@
       <c r="S322" t="n">
         <v>0</v>
       </c>
+      <c r="T322" t="n">
+        <v>57.1428571428571</v>
+      </c>
+      <c r="U322" t="n">
+        <v>42.8571428571428</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -19517,6 +21453,12 @@
       <c r="S323" t="n">
         <v>0</v>
       </c>
+      <c r="T323" t="n">
+        <v>100</v>
+      </c>
+      <c r="U323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -19576,6 +21518,12 @@
       <c r="S324" t="n">
         <v>0</v>
       </c>
+      <c r="T324" t="n">
+        <v>100</v>
+      </c>
+      <c r="U324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -19635,6 +21583,12 @@
       <c r="S325" t="n">
         <v>4</v>
       </c>
+      <c r="T325" t="n">
+        <v>0</v>
+      </c>
+      <c r="U325" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -19694,6 +21648,12 @@
       <c r="S326" t="n">
         <v>0</v>
       </c>
+      <c r="T326" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U326" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -19753,6 +21713,12 @@
       <c r="S327" t="n">
         <v>0</v>
       </c>
+      <c r="T327" t="n">
+        <v>100</v>
+      </c>
+      <c r="U327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -19812,6 +21778,12 @@
       <c r="S328" t="n">
         <v>1</v>
       </c>
+      <c r="T328" t="n">
+        <v>100</v>
+      </c>
+      <c r="U328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -19871,6 +21843,12 @@
       <c r="S329" t="n">
         <v>3</v>
       </c>
+      <c r="T329" t="n">
+        <v>75</v>
+      </c>
+      <c r="U329" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -19930,6 +21908,12 @@
       <c r="S330" t="n">
         <v>2</v>
       </c>
+      <c r="T330" t="n">
+        <v>100</v>
+      </c>
+      <c r="U330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -19989,6 +21973,12 @@
       <c r="S331" t="n">
         <v>0</v>
       </c>
+      <c r="T331" t="n">
+        <v>100</v>
+      </c>
+      <c r="U331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -20048,6 +22038,12 @@
       <c r="S332" t="n">
         <v>0</v>
       </c>
+      <c r="T332" t="n">
+        <v>75</v>
+      </c>
+      <c r="U332" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -20107,6 +22103,12 @@
       <c r="S333" t="n">
         <v>0</v>
       </c>
+      <c r="T333" t="n">
+        <v>100</v>
+      </c>
+      <c r="U333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -20166,6 +22168,12 @@
       <c r="S334" t="n">
         <v>2</v>
       </c>
+      <c r="T334" t="n">
+        <v>75</v>
+      </c>
+      <c r="U334" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -20225,6 +22233,12 @@
       <c r="S335" t="n">
         <v>0</v>
       </c>
+      <c r="T335" t="n">
+        <v>100</v>
+      </c>
+      <c r="U335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -20284,6 +22298,12 @@
       <c r="S336" t="n">
         <v>0</v>
       </c>
+      <c r="T336" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U336" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -20343,6 +22363,12 @@
       <c r="S337" t="n">
         <v>0</v>
       </c>
+      <c r="T337" t="n">
+        <v>0</v>
+      </c>
+      <c r="U337" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -20402,6 +22428,12 @@
       <c r="S338" t="n">
         <v>0</v>
       </c>
+      <c r="T338" t="n">
+        <v>100</v>
+      </c>
+      <c r="U338" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -20461,6 +22493,12 @@
       <c r="S339" t="n">
         <v>0</v>
       </c>
+      <c r="T339" t="n">
+        <v>0</v>
+      </c>
+      <c r="U339" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -20520,6 +22558,12 @@
       <c r="S340" t="n">
         <v>1</v>
       </c>
+      <c r="T340" t="n">
+        <v>100</v>
+      </c>
+      <c r="U340" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -20579,6 +22623,12 @@
       <c r="S341" t="n">
         <v>1</v>
       </c>
+      <c r="T341" t="n">
+        <v>50</v>
+      </c>
+      <c r="U341" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -20638,6 +22688,12 @@
       <c r="S342" t="n">
         <v>1</v>
       </c>
+      <c r="T342" t="n">
+        <v>0</v>
+      </c>
+      <c r="U342" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -20697,6 +22753,12 @@
       <c r="S343" t="n">
         <v>0</v>
       </c>
+      <c r="T343" t="n">
+        <v>50</v>
+      </c>
+      <c r="U343" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -20756,6 +22818,12 @@
       <c r="S344" t="n">
         <v>0</v>
       </c>
+      <c r="T344" t="n">
+        <v>100</v>
+      </c>
+      <c r="U344" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -20815,6 +22883,12 @@
       <c r="S345" t="n">
         <v>2</v>
       </c>
+      <c r="T345" t="n">
+        <v>50</v>
+      </c>
+      <c r="U345" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -20874,6 +22948,12 @@
       <c r="S346" t="n">
         <v>0</v>
       </c>
+      <c r="T346" t="n">
+        <v>100</v>
+      </c>
+      <c r="U346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -20933,6 +23013,12 @@
       <c r="S347" t="n">
         <v>0</v>
       </c>
+      <c r="T347" t="n">
+        <v>100</v>
+      </c>
+      <c r="U347" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -20992,6 +23078,12 @@
       <c r="S348" t="n">
         <v>0</v>
       </c>
+      <c r="T348" t="n">
+        <v>100</v>
+      </c>
+      <c r="U348" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -21051,6 +23143,12 @@
       <c r="S349" t="n">
         <v>1</v>
       </c>
+      <c r="T349" t="n">
+        <v>100</v>
+      </c>
+      <c r="U349" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -21110,6 +23208,12 @@
       <c r="S350" t="n">
         <v>0</v>
       </c>
+      <c r="T350" t="n">
+        <v>75</v>
+      </c>
+      <c r="U350" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -21169,6 +23273,12 @@
       <c r="S351" t="n">
         <v>0</v>
       </c>
+      <c r="T351" t="n">
+        <v>100</v>
+      </c>
+      <c r="U351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -21228,6 +23338,12 @@
       <c r="S352" t="n">
         <v>0</v>
       </c>
+      <c r="T352" t="n">
+        <v>0</v>
+      </c>
+      <c r="U352" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -21287,6 +23403,12 @@
       <c r="S353" t="n">
         <v>0</v>
       </c>
+      <c r="T353" t="n">
+        <v>50</v>
+      </c>
+      <c r="U353" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -21346,6 +23468,12 @@
       <c r="S354" t="n">
         <v>0</v>
       </c>
+      <c r="T354" t="n">
+        <v>100</v>
+      </c>
+      <c r="U354" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -21405,6 +23533,12 @@
       <c r="S355" t="n">
         <v>0</v>
       </c>
+      <c r="T355" t="n">
+        <v>100</v>
+      </c>
+      <c r="U355" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -21464,6 +23598,12 @@
       <c r="S356" t="n">
         <v>0</v>
       </c>
+      <c r="T356" t="n">
+        <v>75</v>
+      </c>
+      <c r="U356" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -21523,6 +23663,12 @@
       <c r="S357" t="n">
         <v>0</v>
       </c>
+      <c r="T357" t="n">
+        <v>57.1428571428571</v>
+      </c>
+      <c r="U357" t="n">
+        <v>42.8571428571428</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -21582,6 +23728,12 @@
       <c r="S358" t="n">
         <v>0</v>
       </c>
+      <c r="T358" t="n">
+        <v>100</v>
+      </c>
+      <c r="U358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -21641,6 +23793,12 @@
       <c r="S359" t="n">
         <v>0</v>
       </c>
+      <c r="T359" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="U359" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -21700,6 +23858,12 @@
       <c r="S360" t="n">
         <v>0</v>
       </c>
+      <c r="T360" t="n">
+        <v>100</v>
+      </c>
+      <c r="U360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -21759,6 +23923,12 @@
       <c r="S361" t="n">
         <v>0</v>
       </c>
+      <c r="T361" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U361" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -21818,6 +23988,12 @@
       <c r="S362" t="n">
         <v>0</v>
       </c>
+      <c r="T362" t="n">
+        <v>100</v>
+      </c>
+      <c r="U362" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -21877,6 +24053,12 @@
       <c r="S363" t="n">
         <v>0</v>
       </c>
+      <c r="T363" t="n">
+        <v>100</v>
+      </c>
+      <c r="U363" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -21936,6 +24118,12 @@
       <c r="S364" t="n">
         <v>0</v>
       </c>
+      <c r="T364" t="n">
+        <v>100</v>
+      </c>
+      <c r="U364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -21995,6 +24183,12 @@
       <c r="S365" t="n">
         <v>0</v>
       </c>
+      <c r="T365" t="n">
+        <v>100</v>
+      </c>
+      <c r="U365" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -22054,6 +24248,12 @@
       <c r="S366" t="n">
         <v>0</v>
       </c>
+      <c r="T366" t="n">
+        <v>50</v>
+      </c>
+      <c r="U366" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -22113,6 +24313,12 @@
       <c r="S367" t="n">
         <v>0</v>
       </c>
+      <c r="T367" t="n">
+        <v>20</v>
+      </c>
+      <c r="U367" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -22172,6 +24378,12 @@
       <c r="S368" t="n">
         <v>0</v>
       </c>
+      <c r="T368" t="n">
+        <v>16.6666666666666</v>
+      </c>
+      <c r="U368" t="n">
+        <v>83.3333333333333</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -22231,6 +24443,12 @@
       <c r="S369" t="n">
         <v>0</v>
       </c>
+      <c r="T369" t="n">
+        <v>16.6666666666666</v>
+      </c>
+      <c r="U369" t="n">
+        <v>83.3333333333333</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -22290,6 +24508,12 @@
       <c r="S370" t="n">
         <v>0</v>
       </c>
+      <c r="T370" t="n">
+        <v>100</v>
+      </c>
+      <c r="U370" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -22349,6 +24573,12 @@
       <c r="S371" t="n">
         <v>0</v>
       </c>
+      <c r="T371" t="n">
+        <v>100</v>
+      </c>
+      <c r="U371" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -22408,6 +24638,12 @@
       <c r="S372" t="n">
         <v>0</v>
       </c>
+      <c r="T372" t="n">
+        <v>100</v>
+      </c>
+      <c r="U372" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -22467,6 +24703,12 @@
       <c r="S373" t="n">
         <v>0</v>
       </c>
+      <c r="T373" t="n">
+        <v>100</v>
+      </c>
+      <c r="U373" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -22526,6 +24768,12 @@
       <c r="S374" t="n">
         <v>0</v>
       </c>
+      <c r="T374" t="n">
+        <v>60</v>
+      </c>
+      <c r="U374" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -22585,6 +24833,12 @@
       <c r="S375" t="n">
         <v>0</v>
       </c>
+      <c r="T375" t="n">
+        <v>100</v>
+      </c>
+      <c r="U375" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -22644,6 +24898,12 @@
       <c r="S376" t="n">
         <v>0</v>
       </c>
+      <c r="T376" t="n">
+        <v>100</v>
+      </c>
+      <c r="U376" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -22703,6 +24963,12 @@
       <c r="S377" t="n">
         <v>0</v>
       </c>
+      <c r="T377" t="n">
+        <v>100</v>
+      </c>
+      <c r="U377" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -22762,6 +25028,12 @@
       <c r="S378" t="n">
         <v>0</v>
       </c>
+      <c r="T378" t="n">
+        <v>100</v>
+      </c>
+      <c r="U378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -22821,6 +25093,12 @@
       <c r="S379" t="n">
         <v>0</v>
       </c>
+      <c r="T379" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U379" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -22880,6 +25158,12 @@
       <c r="S380" t="n">
         <v>0</v>
       </c>
+      <c r="T380" t="n">
+        <v>100</v>
+      </c>
+      <c r="U380" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -22939,6 +25223,12 @@
       <c r="S381" t="n">
         <v>0</v>
       </c>
+      <c r="T381" t="n">
+        <v>100</v>
+      </c>
+      <c r="U381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -22998,6 +25288,12 @@
       <c r="S382" t="n">
         <v>1</v>
       </c>
+      <c r="T382" t="n">
+        <v>100</v>
+      </c>
+      <c r="U382" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -23057,6 +25353,12 @@
       <c r="S383" t="n">
         <v>0</v>
       </c>
+      <c r="T383" t="n">
+        <v>81.8181818181818</v>
+      </c>
+      <c r="U383" t="n">
+        <v>18.1818181818181</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -23116,6 +25418,12 @@
       <c r="S384" t="n">
         <v>0</v>
       </c>
+      <c r="T384" t="n">
+        <v>100</v>
+      </c>
+      <c r="U384" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -23175,6 +25483,12 @@
       <c r="S385" t="n">
         <v>0</v>
       </c>
+      <c r="T385" t="n">
+        <v>50</v>
+      </c>
+      <c r="U385" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -23234,6 +25548,12 @@
       <c r="S386" t="n">
         <v>0</v>
       </c>
+      <c r="T386" t="n">
+        <v>100</v>
+      </c>
+      <c r="U386" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -23293,6 +25613,12 @@
       <c r="S387" t="n">
         <v>0</v>
       </c>
+      <c r="T387" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U387" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -23352,6 +25678,12 @@
       <c r="S388" t="n">
         <v>0</v>
       </c>
+      <c r="T388" t="n">
+        <v>100</v>
+      </c>
+      <c r="U388" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -23411,6 +25743,12 @@
       <c r="S389" t="n">
         <v>0</v>
       </c>
+      <c r="T389" t="n">
+        <v>100</v>
+      </c>
+      <c r="U389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -23470,6 +25808,12 @@
       <c r="S390" t="n">
         <v>0</v>
       </c>
+      <c r="T390" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U390" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -23529,6 +25873,12 @@
       <c r="S391" t="n">
         <v>0</v>
       </c>
+      <c r="T391" t="n">
+        <v>100</v>
+      </c>
+      <c r="U391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -23588,6 +25938,12 @@
       <c r="S392" t="n">
         <v>0</v>
       </c>
+      <c r="T392" t="n">
+        <v>100</v>
+      </c>
+      <c r="U392" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -23647,6 +26003,12 @@
       <c r="S393" t="n">
         <v>0</v>
       </c>
+      <c r="T393" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U393" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -23706,6 +26068,12 @@
       <c r="S394" t="n">
         <v>0</v>
       </c>
+      <c r="T394" t="n">
+        <v>100</v>
+      </c>
+      <c r="U394" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -23765,6 +26133,12 @@
       <c r="S395" t="n">
         <v>0</v>
       </c>
+      <c r="T395" t="n">
+        <v>100</v>
+      </c>
+      <c r="U395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -23824,6 +26198,12 @@
       <c r="S396" t="n">
         <v>0</v>
       </c>
+      <c r="T396" t="n">
+        <v>100</v>
+      </c>
+      <c r="U396" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -23883,6 +26263,12 @@
       <c r="S397" t="n">
         <v>0</v>
       </c>
+      <c r="T397" t="n">
+        <v>100</v>
+      </c>
+      <c r="U397" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -23942,6 +26328,12 @@
       <c r="S398" t="n">
         <v>1</v>
       </c>
+      <c r="T398" t="n">
+        <v>50</v>
+      </c>
+      <c r="U398" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -24001,6 +26393,12 @@
       <c r="S399" t="n">
         <v>0</v>
       </c>
+      <c r="T399" t="n">
+        <v>50</v>
+      </c>
+      <c r="U399" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -24060,6 +26458,12 @@
       <c r="S400" t="n">
         <v>0</v>
       </c>
+      <c r="T400" t="n">
+        <v>0</v>
+      </c>
+      <c r="U400" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -24119,6 +26523,12 @@
       <c r="S401" t="n">
         <v>0</v>
       </c>
+      <c r="T401" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U401" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -24178,6 +26588,12 @@
       <c r="S402" t="n">
         <v>2</v>
       </c>
+      <c r="T402" t="n">
+        <v>100</v>
+      </c>
+      <c r="U402" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -24237,6 +26653,12 @@
       <c r="S403" t="n">
         <v>0</v>
       </c>
+      <c r="T403" t="n">
+        <v>100</v>
+      </c>
+      <c r="U403" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -24296,6 +26718,12 @@
       <c r="S404" t="n">
         <v>0</v>
       </c>
+      <c r="T404" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U404" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -24355,6 +26783,12 @@
       <c r="S405" t="n">
         <v>0</v>
       </c>
+      <c r="T405" t="n">
+        <v>75</v>
+      </c>
+      <c r="U405" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -24414,6 +26848,12 @@
       <c r="S406" t="n">
         <v>0</v>
       </c>
+      <c r="T406" t="n">
+        <v>100</v>
+      </c>
+      <c r="U406" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -24473,6 +26913,12 @@
       <c r="S407" t="n">
         <v>0</v>
       </c>
+      <c r="T407" t="n">
+        <v>100</v>
+      </c>
+      <c r="U407" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -24532,6 +26978,12 @@
       <c r="S408" t="n">
         <v>0</v>
       </c>
+      <c r="T408" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U408" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -24591,6 +27043,12 @@
       <c r="S409" t="n">
         <v>0</v>
       </c>
+      <c r="T409" t="n">
+        <v>100</v>
+      </c>
+      <c r="U409" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -24650,6 +27108,12 @@
       <c r="S410" t="n">
         <v>1</v>
       </c>
+      <c r="T410" t="n">
+        <v>100</v>
+      </c>
+      <c r="U410" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -24709,6 +27173,12 @@
       <c r="S411" t="n">
         <v>0</v>
       </c>
+      <c r="T411" t="n">
+        <v>100</v>
+      </c>
+      <c r="U411" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -24768,6 +27238,12 @@
       <c r="S412" t="n">
         <v>0</v>
       </c>
+      <c r="T412" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U412" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -24827,6 +27303,12 @@
       <c r="S413" t="n">
         <v>0</v>
       </c>
+      <c r="T413" t="n">
+        <v>100</v>
+      </c>
+      <c r="U413" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -24886,6 +27368,12 @@
       <c r="S414" t="n">
         <v>0</v>
       </c>
+      <c r="T414" t="n">
+        <v>100</v>
+      </c>
+      <c r="U414" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -24945,6 +27433,12 @@
       <c r="S415" t="n">
         <v>0</v>
       </c>
+      <c r="T415" t="n">
+        <v>100</v>
+      </c>
+      <c r="U415" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
@@ -25004,6 +27498,12 @@
       <c r="S416" t="n">
         <v>0</v>
       </c>
+      <c r="T416" t="n">
+        <v>100</v>
+      </c>
+      <c r="U416" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
@@ -25063,6 +27563,12 @@
       <c r="S417" t="n">
         <v>0</v>
       </c>
+      <c r="T417" t="n">
+        <v>100</v>
+      </c>
+      <c r="U417" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
@@ -25122,6 +27628,12 @@
       <c r="S418" t="n">
         <v>1</v>
       </c>
+      <c r="T418" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U418" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
@@ -25181,6 +27693,12 @@
       <c r="S419" t="n">
         <v>0</v>
       </c>
+      <c r="T419" t="n">
+        <v>100</v>
+      </c>
+      <c r="U419" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
@@ -25240,6 +27758,12 @@
       <c r="S420" t="n">
         <v>0</v>
       </c>
+      <c r="T420" t="n">
+        <v>100</v>
+      </c>
+      <c r="U420" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
@@ -25299,6 +27823,12 @@
       <c r="S421" t="n">
         <v>0</v>
       </c>
+      <c r="T421" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U421" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
@@ -25358,6 +27888,12 @@
       <c r="S422" t="n">
         <v>0</v>
       </c>
+      <c r="T422" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U422" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
@@ -25417,6 +27953,12 @@
       <c r="S423" t="n">
         <v>0</v>
       </c>
+      <c r="T423" t="n">
+        <v>100</v>
+      </c>
+      <c r="U423" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
@@ -25476,6 +28018,12 @@
       <c r="S424" t="n">
         <v>0</v>
       </c>
+      <c r="T424" t="n">
+        <v>100</v>
+      </c>
+      <c r="U424" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
@@ -25535,6 +28083,12 @@
       <c r="S425" t="n">
         <v>0</v>
       </c>
+      <c r="T425" t="n">
+        <v>60</v>
+      </c>
+      <c r="U425" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
@@ -25594,6 +28148,12 @@
       <c r="S426" t="n">
         <v>0</v>
       </c>
+      <c r="T426" t="n">
+        <v>50</v>
+      </c>
+      <c r="U426" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
@@ -25653,6 +28213,12 @@
       <c r="S427" t="n">
         <v>0</v>
       </c>
+      <c r="T427" t="n">
+        <v>0</v>
+      </c>
+      <c r="U427" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
@@ -25712,6 +28278,12 @@
       <c r="S428" t="n">
         <v>0</v>
       </c>
+      <c r="T428" t="n">
+        <v>100</v>
+      </c>
+      <c r="U428" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
@@ -25771,6 +28343,12 @@
       <c r="S429" t="n">
         <v>0</v>
       </c>
+      <c r="T429" t="n">
+        <v>100</v>
+      </c>
+      <c r="U429" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
@@ -25830,6 +28408,12 @@
       <c r="S430" t="n">
         <v>0</v>
       </c>
+      <c r="T430" t="n">
+        <v>100</v>
+      </c>
+      <c r="U430" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
@@ -25889,6 +28473,12 @@
       <c r="S431" t="n">
         <v>0</v>
       </c>
+      <c r="T431" t="n">
+        <v>100</v>
+      </c>
+      <c r="U431" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
@@ -25948,6 +28538,12 @@
       <c r="S432" t="n">
         <v>0</v>
       </c>
+      <c r="T432" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U432" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
@@ -26007,6 +28603,12 @@
       <c r="S433" t="n">
         <v>0</v>
       </c>
+      <c r="T433" t="n">
+        <v>100</v>
+      </c>
+      <c r="U433" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
@@ -26066,6 +28668,12 @@
       <c r="S434" t="n">
         <v>0</v>
       </c>
+      <c r="T434" t="n">
+        <v>100</v>
+      </c>
+      <c r="U434" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
@@ -26125,6 +28733,12 @@
       <c r="S435" t="n">
         <v>0</v>
       </c>
+      <c r="T435" t="n">
+        <v>75</v>
+      </c>
+      <c r="U435" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
@@ -26184,6 +28798,12 @@
       <c r="S436" t="n">
         <v>0</v>
       </c>
+      <c r="T436" t="n">
+        <v>100</v>
+      </c>
+      <c r="U436" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
@@ -26243,6 +28863,12 @@
       <c r="S437" t="n">
         <v>0</v>
       </c>
+      <c r="T437" t="n">
+        <v>0</v>
+      </c>
+      <c r="U437" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
@@ -26302,6 +28928,12 @@
       <c r="S438" t="n">
         <v>0</v>
       </c>
+      <c r="T438" t="n">
+        <v>50</v>
+      </c>
+      <c r="U438" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
@@ -26361,6 +28993,12 @@
       <c r="S439" t="n">
         <v>0</v>
       </c>
+      <c r="T439" t="n">
+        <v>50</v>
+      </c>
+      <c r="U439" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
@@ -26420,6 +29058,12 @@
       <c r="S440" t="n">
         <v>2</v>
       </c>
+      <c r="T440" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U440" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
@@ -26479,6 +29123,12 @@
       <c r="S441" t="n">
         <v>0</v>
       </c>
+      <c r="T441" t="n">
+        <v>100</v>
+      </c>
+      <c r="U441" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
@@ -26538,6 +29188,12 @@
       <c r="S442" t="n">
         <v>0</v>
       </c>
+      <c r="T442" t="n">
+        <v>100</v>
+      </c>
+      <c r="U442" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
@@ -26597,6 +29253,12 @@
       <c r="S443" t="n">
         <v>0</v>
       </c>
+      <c r="T443" t="n">
+        <v>50</v>
+      </c>
+      <c r="U443" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
@@ -26656,6 +29318,12 @@
       <c r="S444" t="n">
         <v>0</v>
       </c>
+      <c r="T444" t="n">
+        <v>100</v>
+      </c>
+      <c r="U444" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
@@ -26715,6 +29383,12 @@
       <c r="S445" t="n">
         <v>0</v>
       </c>
+      <c r="T445" t="n">
+        <v>100</v>
+      </c>
+      <c r="U445" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
@@ -26774,6 +29448,12 @@
       <c r="S446" t="n">
         <v>0</v>
       </c>
+      <c r="T446" t="n">
+        <v>100</v>
+      </c>
+      <c r="U446" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
@@ -26833,6 +29513,12 @@
       <c r="S447" t="n">
         <v>0</v>
       </c>
+      <c r="T447" t="n">
+        <v>100</v>
+      </c>
+      <c r="U447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
@@ -26892,6 +29578,12 @@
       <c r="S448" t="n">
         <v>0</v>
       </c>
+      <c r="T448" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U448" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
@@ -26951,6 +29643,12 @@
       <c r="S449" t="n">
         <v>0</v>
       </c>
+      <c r="T449" t="n">
+        <v>50</v>
+      </c>
+      <c r="U449" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
@@ -27010,6 +29708,12 @@
       <c r="S450" t="n">
         <v>0</v>
       </c>
+      <c r="T450" t="n">
+        <v>50</v>
+      </c>
+      <c r="U450" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
@@ -27069,6 +29773,12 @@
       <c r="S451" t="n">
         <v>0</v>
       </c>
+      <c r="T451" t="n">
+        <v>75</v>
+      </c>
+      <c r="U451" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
@@ -27128,6 +29838,12 @@
       <c r="S452" t="n">
         <v>0</v>
       </c>
+      <c r="T452" t="n">
+        <v>75</v>
+      </c>
+      <c r="U452" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
@@ -27187,6 +29903,12 @@
       <c r="S453" t="n">
         <v>0</v>
       </c>
+      <c r="T453" t="n">
+        <v>100</v>
+      </c>
+      <c r="U453" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
@@ -27246,6 +29968,12 @@
       <c r="S454" t="n">
         <v>0</v>
       </c>
+      <c r="T454" t="n">
+        <v>100</v>
+      </c>
+      <c r="U454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
@@ -27305,6 +30033,12 @@
       <c r="S455" t="n">
         <v>0</v>
       </c>
+      <c r="T455" t="n">
+        <v>75</v>
+      </c>
+      <c r="U455" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
@@ -27364,6 +30098,12 @@
       <c r="S456" t="n">
         <v>0</v>
       </c>
+      <c r="T456" t="n">
+        <v>80</v>
+      </c>
+      <c r="U456" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
@@ -27422,6 +30162,12 @@
       </c>
       <c r="S457" t="n">
         <v>0</v>
+      </c>
+      <c r="T457" t="n">
+        <v>75</v>
+      </c>
+      <c r="U457" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
